--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -26,33 +26,6 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>作者</author>
-  </authors>
-  <commentList>
-    <comment ref="D3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color rgb="FF000000"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 攻击性
-2 恢复性
-3 全能型</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="Item_Template" type="4" background="1" refreshedVersion="2" saveData="1">
@@ -62,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="101">
   <si>
     <t>c</t>
   </si>
@@ -70,7 +43,7 @@
     <t>Id</t>
   </si>
   <si>
-    <t>生命之盾类型</t>
+    <t>位置</t>
   </si>
   <si>
     <t>名字</t>
@@ -82,7 +55,10 @@
     <t>等级</t>
   </si>
   <si>
-    <t>生命之盾经验</t>
+    <t>开启消耗道具</t>
+  </si>
+  <si>
+    <t>开启需要总等级</t>
   </si>
   <si>
     <t>额外属性</t>
@@ -94,19 +70,22 @@
     <t>额外描述2</t>
   </si>
   <si>
-    <t>ShieldType</t>
-  </si>
-  <si>
-    <t>ShieldName</t>
+    <t>Position</t>
+  </si>
+  <si>
+    <t>MagicName</t>
   </si>
   <si>
     <t>ShieldName_EN</t>
   </si>
   <si>
-    <t>ShieldLevel</t>
-  </si>
-  <si>
-    <t>ShieldExp</t>
+    <t>MagicLevel</t>
+  </si>
+  <si>
+    <t>OpenCostItem</t>
+  </si>
+  <si>
+    <t>NeedTotalLevel</t>
   </si>
   <si>
     <t>AddProperty</t>
@@ -124,12 +103,15 @@
     <t>string</t>
   </si>
   <si>
-    <t>熔岩之魂1级</t>
+    <t>一号位攻击型魔能1级</t>
   </si>
   <si>
     <t>Lava Soul Level 1</t>
   </si>
   <si>
+    <t>10000165;1@10000166;1</t>
+  </si>
+  <si>
     <t>205703;0.01</t>
   </si>
   <si>
@@ -139,7 +121,7 @@
     <t>Reduces damage taken from player basic attacks by 1%.</t>
   </si>
   <si>
-    <t>熔岩之魂2级</t>
+    <t>一号位攻击型魔能2级</t>
   </si>
   <si>
     <t>Lava Soul Level 2</t>
@@ -152,6 +134,210 @@
   </si>
   <si>
     <t>Reduce damage from player's normal attacks by 2%</t>
+  </si>
+  <si>
+    <t>一号位攻击型魔能3级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 3</t>
+  </si>
+  <si>
+    <t>205703;0.03</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害3%</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 2%.</t>
+  </si>
+  <si>
+    <t>一号位攻击型魔能4级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 4</t>
+  </si>
+  <si>
+    <t>205703;0.04</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害4%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 3%</t>
+  </si>
+  <si>
+    <t>一号位攻击型魔能5级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 5</t>
+  </si>
+  <si>
+    <t>205703;0.05</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害5%</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 3%.</t>
+  </si>
+  <si>
+    <t>一号位攻击型魔能6级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 6</t>
+  </si>
+  <si>
+    <t>205703;0.06</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害6%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 4%</t>
+  </si>
+  <si>
+    <t>一号位攻击型魔能7级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 7</t>
+  </si>
+  <si>
+    <t>205703;0.07</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害7%</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 4%.</t>
+  </si>
+  <si>
+    <t>一号位攻击型魔能8级</t>
+  </si>
+  <si>
+    <t>Lava Soul Level 8</t>
+  </si>
+  <si>
+    <t>205703;0.08</t>
+  </si>
+  <si>
+    <t>降低受到玩家普通攻击伤害8%</t>
+  </si>
+  <si>
+    <t>Reduce damage from player's normal attacks by 5%</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能1级</t>
+  </si>
+  <si>
+    <t>205803;0.01</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能2级</t>
+  </si>
+  <si>
+    <t>205803;0.02</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能3级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;2</t>
+  </si>
+  <si>
+    <t>205803;0.03</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能4级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;3</t>
+  </si>
+  <si>
+    <t>205803;0.04</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能5级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;4</t>
+  </si>
+  <si>
+    <t>205803;0.05</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 5%.</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能6级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;5</t>
+  </si>
+  <si>
+    <t>205803;0.06</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 6%.</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能7级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;6</t>
+  </si>
+  <si>
+    <t>205803;0.07</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 7%.</t>
+  </si>
+  <si>
+    <t>二号位攻击型魔能8级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;7</t>
+  </si>
+  <si>
+    <t>205803;0.08</t>
+  </si>
+  <si>
+    <t>Reduces damage taken from player basic attacks by 8%.</t>
+  </si>
+  <si>
+    <t>三号位攻击型魔能1级</t>
+  </si>
+  <si>
+    <t>三号位攻击型魔能2级</t>
+  </si>
+  <si>
+    <t>10000165;1@10000166;8</t>
+  </si>
+  <si>
+    <t>一号位恢复型魔能1级</t>
+  </si>
+  <si>
+    <t>二号位恢复型魔能1级</t>
+  </si>
+  <si>
+    <t>三号位恢复型魔能1级</t>
+  </si>
+  <si>
+    <t>一号位全能型魔能1级</t>
+  </si>
+  <si>
+    <t>一号位全能型魔能2级</t>
+  </si>
+  <si>
+    <t>二号位全能型魔能1级</t>
+  </si>
+  <si>
+    <t>二号位全能型魔能2级</t>
+  </si>
+  <si>
+    <t>三号位全能型魔能1级</t>
+  </si>
+  <si>
+    <t>三号位全能型魔能2级</t>
   </si>
 </sst>
 </file>
@@ -164,7 +350,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -177,13 +363,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -349,15 +528,8 @@
       <name val="Tahoma"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="48">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -595,48 +767,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799798577837458"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -819,1061 +949,1061 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="47" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1883,20 +2013,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2338,7 +2468,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{773FC13B-7C21-4A26-A7CE-86C5170285A8}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{335EC9DB-8391-4DC5-B35F-319CD6394E47}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
@@ -2381,18 +2511,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:K7" totalsRowShown="0">
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:L7" totalsRowShown="0">
+  <tableColumns count="10">
     <tableColumn id="1" name="Id">
       <calculatedColumnFormula>C3+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" name="生命之盾类型"/>
+    <tableColumn id="10" name="位置"/>
     <tableColumn id="3" name="名字"/>
     <tableColumn id="8" name="名字2" dataDxfId="0"/>
     <tableColumn id="4" name="等级">
       <calculatedColumnFormula>G3+1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="生命之盾经验"/>
+    <tableColumn id="2" name="开启消耗道具"/>
+    <tableColumn id="11" name="开启需要总等级"/>
     <tableColumn id="6" name="额外属性"/>
     <tableColumn id="7" name="额外描述">
       <calculatedColumnFormula>"生命上限提升+"&amp;G4&amp;"%,眩晕抵抗概率+"&amp;G4&amp;"%"</calculatedColumnFormula>
@@ -2688,28 +2819,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:K222"/>
+  <dimension ref="C1:L35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="21.625" customWidth="1"/>
-    <col min="4" max="8" width="28.875" customWidth="1"/>
-    <col min="9" max="9" width="27.25" style="1" customWidth="1"/>
-    <col min="10" max="11" width="53.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="15.375" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="19.875" customWidth="1"/>
+    <col min="7" max="7" width="17.375" customWidth="1"/>
+    <col min="8" max="8" width="19.75" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="10" max="10" width="18" style="1" customWidth="1"/>
+    <col min="11" max="11" width="34" style="1" customWidth="1"/>
+    <col min="12" max="12" width="36.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="6:11">
+    <row r="2" ht="20.1" customHeight="1" spans="6:12">
       <c r="F2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>0</v>
-      </c>
       <c r="K2" s="7" t="s">
         <v>0</v>
       </c>
+      <c r="L2" s="7" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
+    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C3" s="4" t="s">
         <v>1</v>
       </c>
@@ -2728,7 +2865,7 @@
       <c r="H3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="J3" s="5" t="s">
@@ -2737,66 +2874,75 @@
       <c r="K3" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="L3" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:11">
+    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:12">
       <c r="C5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C6" s="6">
         <v>1001</v>
       </c>
@@ -2804,28 +2950,31 @@
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G6" s="6">
         <v>1</v>
       </c>
-      <c r="H6" s="6">
-        <v>3000</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>23</v>
+      <c r="H6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="6">
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:11">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
       <c r="C7" s="6">
         <v>1002</v>
       </c>
@@ -2833,35 +2982,932 @@
         <v>1</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G7" s="6">
         <v>2</v>
       </c>
-      <c r="H7" s="6">
-        <v>6000</v>
-      </c>
-      <c r="I7" s="6" t="s">
+      <c r="H7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I7" s="6">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C8" s="6">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="6">
+        <v>3</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="6">
+        <v>2</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C9" s="6">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" s="6">
+        <v>4</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I9" s="6">
+        <v>3</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C10" s="6">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="6">
+        <v>5</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="6">
+        <v>4</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C11" s="6">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G11" s="6">
+        <v>6</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I11" s="6">
+        <v>5</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C12" s="6">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="6">
+        <v>7</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I12" s="6">
+        <v>6</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C13" s="6">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="6">
+        <v>8</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I13" s="6">
+        <v>7</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C14" s="6">
+        <v>2001</v>
+      </c>
+      <c r="D14" s="6">
+        <v>2</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="8" t="s">
+    </row>
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C15" s="6">
+        <v>2002</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C16" s="6">
+        <v>2003</v>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="6">
+        <v>3</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="I16" s="6">
+        <v>2</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C17" s="6">
+        <v>2004</v>
+      </c>
+      <c r="D17" s="6">
+        <v>2</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="6">
+        <v>4</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I17" s="6">
+        <v>3</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C18" s="6">
+        <v>2005</v>
+      </c>
+      <c r="D18" s="6">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18" s="6">
+        <v>5</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I18" s="6">
+        <v>4</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C19" s="6">
+        <v>2006</v>
+      </c>
+      <c r="D19" s="6">
+        <v>2</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="G19" s="6">
+        <v>6</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I19" s="6">
+        <v>5</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C20" s="6">
+        <v>2007</v>
+      </c>
+      <c r="D20" s="6">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="6">
+        <v>7</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="6">
+        <v>6</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C21" s="6">
+        <v>2008</v>
+      </c>
+      <c r="D21" s="6">
+        <v>2</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="G21" s="6">
+        <v>8</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="6">
+        <v>7</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C22" s="6">
+        <v>3001</v>
+      </c>
+      <c r="D22" s="6">
+        <v>3</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I22" s="6">
+        <v>7</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C23" s="6">
+        <v>3002</v>
+      </c>
+      <c r="D23" s="6">
+        <v>3</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="6">
+        <v>2</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I23" s="6">
+        <v>8</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C24" s="6">
+        <v>4001</v>
+      </c>
+      <c r="D24" s="6">
+        <v>4</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G24" s="6">
+        <v>1</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I24" s="6">
+        <v>7</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C25" s="6">
+        <v>4002</v>
+      </c>
+      <c r="D25" s="6">
+        <v>4</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="F25" s="6" t="s">
         <v>29</v>
       </c>
+      <c r="G25" s="6">
+        <v>2</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I25" s="6">
+        <v>8</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="222" ht="13.5"/>
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C26" s="6">
+        <v>5001</v>
+      </c>
+      <c r="D26" s="6">
+        <v>5</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I26" s="6">
+        <v>7</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C27" s="6">
+        <v>5002</v>
+      </c>
+      <c r="D27" s="6">
+        <v>5</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="6">
+        <v>2</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="6">
+        <v>8</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C28" s="6">
+        <v>6001</v>
+      </c>
+      <c r="D28" s="6">
+        <v>6</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I28" s="6">
+        <v>7</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C29" s="6">
+        <v>6002</v>
+      </c>
+      <c r="D29" s="6">
+        <v>6</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="6">
+        <v>2</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I29" s="6">
+        <v>8</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C30" s="6">
+        <v>7001</v>
+      </c>
+      <c r="D30" s="6">
+        <v>7</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I30" s="6">
+        <v>7</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C31" s="6">
+        <v>7002</v>
+      </c>
+      <c r="D31" s="6">
+        <v>7</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G31" s="6">
+        <v>2</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I31" s="6">
+        <v>8</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C32" s="6">
+        <v>8001</v>
+      </c>
+      <c r="D32" s="6">
+        <v>8</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G32" s="6">
+        <v>1</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I32" s="6">
+        <v>7</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C33" s="6">
+        <v>8002</v>
+      </c>
+      <c r="D33" s="6">
+        <v>8</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="6">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I33" s="6">
+        <v>8</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C34" s="6">
+        <v>9001</v>
+      </c>
+      <c r="D34" s="6">
+        <v>9</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="6">
+        <v>1</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="I34" s="6">
+        <v>7</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
+      <c r="C35" s="6">
+        <v>9002</v>
+      </c>
+      <c r="D35" s="6">
+        <v>9</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="6">
+        <v>2</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I35" s="6">
+        <v>8</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="103">
   <si>
     <t>c</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Id</t>
   </si>
   <si>
+    <t>魔能类型</t>
+  </si>
+  <si>
     <t>位置</t>
   </si>
   <si>
@@ -68,6 +71,9 @@
   </si>
   <si>
     <t>额外描述2</t>
+  </si>
+  <si>
+    <t>MagicType</t>
   </si>
   <si>
     <t>Position</t>
@@ -2007,23 +2013,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2468,7 +2477,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{335EC9DB-8391-4DC5-B35F-319CD6394E47}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{CD927318-0D92-41E8-85F8-DE00D622D5A5}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
@@ -2511,22 +2520,23 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:L7" totalsRowShown="0">
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:M7" totalsRowShown="0">
+  <tableColumns count="11">
     <tableColumn id="1" name="Id">
       <calculatedColumnFormula>C3+1</calculatedColumnFormula>
     </tableColumn>
+    <tableColumn id="5" name="魔能类型"/>
     <tableColumn id="10" name="位置"/>
     <tableColumn id="3" name="名字"/>
     <tableColumn id="8" name="名字2" dataDxfId="0"/>
     <tableColumn id="4" name="等级">
-      <calculatedColumnFormula>G3+1</calculatedColumnFormula>
+      <calculatedColumnFormula>H3+1</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="2" name="开启消耗道具"/>
     <tableColumn id="11" name="开启需要总等级"/>
     <tableColumn id="6" name="额外属性"/>
     <tableColumn id="7" name="额外描述">
-      <calculatedColumnFormula>"生命上限提升+"&amp;G4&amp;"%,眩晕抵抗概率+"&amp;G4&amp;"%"</calculatedColumnFormula>
+      <calculatedColumnFormula>"生命上限提升+"&amp;H4&amp;"%,眩晕抵抗概率+"&amp;H4&amp;"%"</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="9" name="额外描述2" dataDxfId="1"/>
   </tableColumns>
@@ -2819,1087 +2829,1186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:L35"/>
+  <dimension ref="C1:M35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="21.625" customWidth="1"/>
-    <col min="4" max="4" width="15.375" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="19.875" customWidth="1"/>
-    <col min="7" max="7" width="17.375" customWidth="1"/>
-    <col min="8" max="8" width="19.75" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
-    <col min="10" max="10" width="18" style="1" customWidth="1"/>
-    <col min="11" max="11" width="34" style="1" customWidth="1"/>
-    <col min="12" max="12" width="36.125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="21.625" customWidth="1"/>
+    <col min="5" max="5" width="15.375" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19.875" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
+    <col min="10" max="10" width="19.5" customWidth="1"/>
+    <col min="11" max="11" width="18" style="1" customWidth="1"/>
+    <col min="12" max="12" width="34" style="1" customWidth="1"/>
+    <col min="13" max="13" width="36.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="6:12">
-      <c r="F2" s="3" t="s">
+    <row r="2" ht="20.1" customHeight="1" spans="3:13">
+      <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="M2" s="4" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C3" s="4" t="s">
+    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="M3" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C4" s="4" t="s">
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="J4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="K4" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="L4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:12">
-      <c r="C5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>20</v>
+    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:13">
+      <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="K5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C6" s="6">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C6" s="8">
         <v>1001</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="8">
         <v>1</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="6">
+      <c r="E6" s="8">
         <v>1</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="F6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="6">
+      <c r="G6" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="8">
+        <v>1</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J6" s="8">
         <v>0</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="K6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C7" s="8">
+        <v>1002</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="8">
+        <v>2</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="8">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L7" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C8" s="8">
+        <v>1003</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="8">
+        <v>2</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C9" s="8">
+        <v>1004</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="8">
+        <v>4</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J9" s="8">
+        <v>3</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C10" s="8">
+        <v>1005</v>
+      </c>
+      <c r="D10" s="8">
+        <v>1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="8">
+        <v>5</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J10" s="8">
+        <v>4</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C11" s="8">
+        <v>1006</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" s="8">
+        <v>6</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J11" s="8">
+        <v>5</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C12" s="8">
+        <v>1007</v>
+      </c>
+      <c r="D12" s="8">
+        <v>1</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="8">
+        <v>7</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J12" s="8">
+        <v>6</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="L12" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M12" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C13" s="8">
+        <v>1008</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" s="8">
+        <v>8</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="8">
+        <v>7</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="L13" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C14" s="8">
+        <v>2001</v>
+      </c>
+      <c r="D14" s="8">
+        <v>1</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M14" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C15" s="8">
+        <v>2002</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H15" s="8">
+        <v>2</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J15" s="8">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="L15" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M15" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C16" s="8">
+        <v>2003</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>2</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="8">
+        <v>3</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J16" s="8">
+        <v>2</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="L16" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="M16" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C17" s="8">
+        <v>2004</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>2</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H17" s="8">
+        <v>4</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="8">
+        <v>3</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="L17" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="M17" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C18" s="8">
+        <v>2005</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H18" s="8">
+        <v>5</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="8">
+        <v>4</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="L18" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="M18" s="9" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C19" s="8">
+        <v>2006</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8">
+        <v>2</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="H19" s="8">
+        <v>6</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="8">
+        <v>5</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L19" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="M19" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C20" s="8">
+        <v>2007</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H20" s="8">
+        <v>7</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="J20" s="8">
+        <v>6</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="L20" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="M20" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C21" s="8">
+        <v>2008</v>
+      </c>
+      <c r="D21" s="8">
+        <v>1</v>
+      </c>
+      <c r="E21" s="8">
+        <v>2</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="8">
+        <v>8</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J21" s="8">
+        <v>7</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="L21" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M21" s="9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C22" s="8">
+        <v>3001</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8">
+        <v>3</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="8">
+        <v>1</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J22" s="8">
+        <v>7</v>
+      </c>
+      <c r="K22" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="L22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="9" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C7" s="6">
-        <v>1002</v>
-      </c>
-      <c r="D7" s="6">
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C23" s="8">
+        <v>3002</v>
+      </c>
+      <c r="D23" s="8">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E23" s="8">
+        <v>3</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H23" s="8">
+        <v>2</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J23" s="8">
+        <v>8</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C24" s="8">
+        <v>4001</v>
+      </c>
+      <c r="D24" s="8">
+        <v>2</v>
+      </c>
+      <c r="E24" s="8">
+        <v>4</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="G24" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H24" s="8">
+        <v>1</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J24" s="8">
+        <v>7</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="M24" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G7" s="6">
+    </row>
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C25" s="8">
+        <v>4002</v>
+      </c>
+      <c r="D25" s="8">
         <v>2</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="6">
+      <c r="E25" s="8">
+        <v>4</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="8">
+        <v>2</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J25" s="8">
+        <v>8</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L25" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M25" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C26" s="8">
+        <v>5001</v>
+      </c>
+      <c r="D26" s="8">
+        <v>2</v>
+      </c>
+      <c r="E26" s="8">
+        <v>5</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="8">
         <v>1</v>
       </c>
-      <c r="J7" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="I26" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J26" s="8">
+        <v>7</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L26" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C27" s="8">
+        <v>5002</v>
+      </c>
+      <c r="D27" s="8">
+        <v>2</v>
+      </c>
+      <c r="E27" s="8">
+        <v>5</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G27" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="L7" s="8" t="s">
+      <c r="H27" s="8">
+        <v>2</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J27" s="8">
+        <v>8</v>
+      </c>
+      <c r="K27" s="8" t="s">
         <v>32</v>
       </c>
+      <c r="L27" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M27" s="9" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C8" s="6">
-        <v>1003</v>
-      </c>
-      <c r="D8" s="6">
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C28" s="8">
+        <v>6001</v>
+      </c>
+      <c r="D28" s="8">
+        <v>2</v>
+      </c>
+      <c r="E28" s="8">
+        <v>6</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H28" s="8">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="I28" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J28" s="8">
+        <v>7</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M28" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C29" s="8">
+        <v>6002</v>
+      </c>
+      <c r="D29" s="8">
+        <v>2</v>
+      </c>
+      <c r="E29" s="8">
+        <v>6</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H29" s="8">
+        <v>2</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J29" s="8">
+        <v>8</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L29" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G8" s="6">
+      <c r="M29" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C30" s="8">
+        <v>7001</v>
+      </c>
+      <c r="D30" s="8">
         <v>3</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="6">
+      <c r="E30" s="8">
+        <v>7</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="8">
+        <v>1</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J30" s="8">
+        <v>7</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C31" s="8">
+        <v>7002</v>
+      </c>
+      <c r="D31" s="8">
+        <v>3</v>
+      </c>
+      <c r="E31" s="8">
+        <v>7</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H31" s="8">
         <v>2</v>
       </c>
-      <c r="J8" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>37</v>
+      <c r="I31" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J31" s="8">
+        <v>8</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L31" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M31" s="9" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C9" s="6">
-        <v>1004</v>
-      </c>
-      <c r="D9" s="6">
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C32" s="8">
+        <v>8001</v>
+      </c>
+      <c r="D32" s="8">
+        <v>3</v>
+      </c>
+      <c r="E32" s="8">
+        <v>8</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H32" s="8">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="6" t="s">
+      <c r="I32" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J32" s="8">
+        <v>7</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C33" s="8">
+        <v>8002</v>
+      </c>
+      <c r="D33" s="8">
+        <v>3</v>
+      </c>
+      <c r="E33" s="8">
+        <v>8</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="G33" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H33" s="8">
+        <v>2</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="8">
+        <v>8</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M33" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="6">
-        <v>4</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" s="6">
+    </row>
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C34" s="8">
+        <v>9001</v>
+      </c>
+      <c r="D34" s="8">
         <v>3</v>
       </c>
-      <c r="J9" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>42</v>
+      <c r="E34" s="8">
+        <v>9</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="G34" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="8">
+        <v>1</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="J34" s="8">
+        <v>7</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="L34" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="M34" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C10" s="6">
-        <v>1005</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="6">
-        <v>5</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="6">
-        <v>4</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C11" s="6">
-        <v>1006</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="6">
-        <v>6</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="6">
-        <v>5</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C12" s="6">
-        <v>1007</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="6">
-        <v>7</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="6">
-        <v>6</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C13" s="6">
-        <v>1008</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="6">
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+      <c r="C35" s="8">
+        <v>9002</v>
+      </c>
+      <c r="D35" s="8">
+        <v>3</v>
+      </c>
+      <c r="E35" s="8">
+        <v>9</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G35" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H35" s="8">
+        <v>2</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="J35" s="8">
         <v>8</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="6">
-        <v>7</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C14" s="6">
-        <v>2001</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G14" s="6">
-        <v>1</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="6">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C15" s="6">
-        <v>2002</v>
-      </c>
-      <c r="D15" s="6">
-        <v>2</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G15" s="6">
-        <v>2</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="6">
-        <v>1</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C16" s="6">
-        <v>2003</v>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G16" s="6">
-        <v>3</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="I16" s="6">
-        <v>2</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C17" s="6">
-        <v>2004</v>
-      </c>
-      <c r="D17" s="6">
-        <v>2</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="6">
-        <v>4</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I17" s="6">
-        <v>3</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C18" s="6">
-        <v>2005</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="K35" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="L35" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="G18" s="6">
-        <v>5</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I18" s="6">
-        <v>4</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K18" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C19" s="6">
-        <v>2006</v>
-      </c>
-      <c r="D19" s="6">
-        <v>2</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" s="6">
-        <v>6</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="6">
-        <v>5</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C20" s="6">
-        <v>2007</v>
-      </c>
-      <c r="D20" s="6">
-        <v>2</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G20" s="6">
-        <v>7</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="I20" s="6">
-        <v>6</v>
-      </c>
-      <c r="J20" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="K20" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C21" s="6">
-        <v>2008</v>
-      </c>
-      <c r="D21" s="6">
-        <v>2</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="6">
-        <v>8</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I21" s="6">
-        <v>7</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C22" s="6">
-        <v>3001</v>
-      </c>
-      <c r="D22" s="6">
-        <v>3</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G22" s="6">
-        <v>1</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I22" s="6">
-        <v>7</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C23" s="6">
-        <v>3002</v>
-      </c>
-      <c r="D23" s="6">
-        <v>3</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G23" s="6">
-        <v>2</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I23" s="6">
-        <v>8</v>
-      </c>
-      <c r="J23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C24" s="6">
-        <v>4001</v>
-      </c>
-      <c r="D24" s="6">
-        <v>4</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G24" s="6">
-        <v>1</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I24" s="6">
-        <v>7</v>
-      </c>
-      <c r="J24" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C25" s="6">
-        <v>4002</v>
-      </c>
-      <c r="D25" s="6">
-        <v>4</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G25" s="6">
-        <v>2</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="6">
-        <v>8</v>
-      </c>
-      <c r="J25" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C26" s="6">
-        <v>5001</v>
-      </c>
-      <c r="D26" s="6">
-        <v>5</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G26" s="6">
-        <v>1</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I26" s="6">
-        <v>7</v>
-      </c>
-      <c r="J26" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K26" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C27" s="6">
-        <v>5002</v>
-      </c>
-      <c r="D27" s="6">
-        <v>5</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G27" s="6">
-        <v>2</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I27" s="6">
-        <v>8</v>
-      </c>
-      <c r="J27" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C28" s="6">
-        <v>6001</v>
-      </c>
-      <c r="D28" s="6">
-        <v>6</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G28" s="6">
-        <v>1</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I28" s="6">
-        <v>7</v>
-      </c>
-      <c r="J28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K28" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C29" s="6">
-        <v>6002</v>
-      </c>
-      <c r="D29" s="6">
-        <v>6</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G29" s="6">
-        <v>2</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="6">
-        <v>8</v>
-      </c>
-      <c r="J29" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C30" s="6">
-        <v>7001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>7</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="6">
-        <v>1</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I30" s="6">
-        <v>7</v>
-      </c>
-      <c r="J30" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K30" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C31" s="6">
-        <v>7002</v>
-      </c>
-      <c r="D31" s="6">
-        <v>7</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G31" s="6">
-        <v>2</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I31" s="6">
-        <v>8</v>
-      </c>
-      <c r="J31" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C32" s="6">
-        <v>8001</v>
-      </c>
-      <c r="D32" s="6">
-        <v>8</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G32" s="6">
-        <v>1</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I32" s="6">
-        <v>7</v>
-      </c>
-      <c r="J32" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C33" s="6">
-        <v>8002</v>
-      </c>
-      <c r="D33" s="6">
-        <v>8</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G33" s="6">
-        <v>2</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I33" s="6">
-        <v>8</v>
-      </c>
-      <c r="J33" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C34" s="6">
-        <v>9001</v>
-      </c>
-      <c r="D34" s="6">
-        <v>9</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="G34" s="6">
-        <v>1</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="I34" s="6">
-        <v>7</v>
-      </c>
-      <c r="J34" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K34" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:12">
-      <c r="C35" s="6">
-        <v>9002</v>
-      </c>
-      <c r="D35" s="6">
-        <v>9</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G35" s="6">
-        <v>2</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="I35" s="6">
-        <v>8</v>
-      </c>
-      <c r="J35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="K35" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="108">
   <si>
     <t>c</t>
   </si>
@@ -235,6 +235,9 @@
     <t>二号位攻击型魔能1级</t>
   </si>
   <si>
+    <t>10000165;11@10000166;1</t>
+  </si>
+  <si>
     <t>205803;0.01</t>
   </si>
   <si>
@@ -313,6 +316,9 @@
     <t>三号位攻击型魔能1级</t>
   </si>
   <si>
+    <t>10000165;4@10000166;7</t>
+  </si>
+  <si>
     <t>三号位攻击型魔能2级</t>
   </si>
   <si>
@@ -325,9 +331,15 @@
     <t>二号位恢复型魔能1级</t>
   </si>
   <si>
+    <t>10000165;8@10000166;7</t>
+  </si>
+  <si>
     <t>三号位恢复型魔能1级</t>
   </si>
   <si>
+    <t>10000165;6@10000166;7</t>
+  </si>
+  <si>
     <t>一号位全能型魔能1级</t>
   </si>
   <si>
@@ -341,6 +353,9 @@
   </si>
   <si>
     <t>三号位全能型魔能1级</t>
+  </si>
+  <si>
+    <t>10000165;5@10000166;7</t>
   </si>
   <si>
     <t>三号位全能型魔能2级</t>
@@ -2013,7 +2028,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2024,9 +2039,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2477,7 +2489,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{CD927318-0D92-41E8-85F8-DE00D622D5A5}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{E5649472-DEE2-4855-B30F-1580C0886754}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
@@ -2895,7 +2907,7 @@
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -2962,1052 +2974,1052 @@
       </c>
     </row>
     <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>1001</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>1</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>1</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="8" t="s">
+      <c r="G6" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="7">
         <v>1</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="I6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="7">
         <v>0</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>1002</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="7">
         <v>1</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7" s="7">
         <v>1</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="7">
         <v>2</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>1003</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8" s="7">
         <v>1</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8" s="7">
         <v>1</v>
       </c>
-      <c r="F8" s="8" t="s">
+      <c r="F8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="7">
         <v>3</v>
       </c>
-      <c r="I8" s="8" t="s">
+      <c r="I8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J8" s="8">
+      <c r="J8" s="7">
         <v>2</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>1004</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="7">
         <v>1</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>1</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="7">
         <v>4</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="I9" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="7">
         <v>3</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="8" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>1005</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10" s="7">
         <v>1</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10" s="7">
         <v>1</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="8" t="s">
+      <c r="G10" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>5</v>
       </c>
-      <c r="I10" s="8" t="s">
+      <c r="I10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="7">
         <v>4</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>1006</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11" s="7">
         <v>1</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>1</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="F11" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>6</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="7">
         <v>5</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="8" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C12" s="8">
+      <c r="C12" s="7">
         <v>1007</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="7">
         <v>1</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12" s="7">
         <v>1</v>
       </c>
-      <c r="F12" s="8" t="s">
+      <c r="F12" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="7">
         <v>7</v>
       </c>
-      <c r="I12" s="8" t="s">
+      <c r="I12" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="7">
         <v>6</v>
       </c>
-      <c r="K12" s="8" t="s">
+      <c r="K12" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>1008</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13" s="7">
         <v>1</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13" s="7">
         <v>1</v>
       </c>
-      <c r="F13" s="8" t="s">
+      <c r="F13" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="7">
         <v>8</v>
       </c>
-      <c r="I13" s="8" t="s">
+      <c r="I13" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="7">
         <v>7</v>
       </c>
-      <c r="K13" s="8" t="s">
+      <c r="K13" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="L13" s="9" t="s">
+      <c r="L13" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="8" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>2001</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="7">
         <v>1</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>2</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="7">
         <v>1</v>
       </c>
-      <c r="I14" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="J14" s="8">
+      <c r="I14" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J14" s="7">
         <v>0</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="9" t="s">
+      <c r="K14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>2002</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="7">
         <v>1</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="7">
         <v>2</v>
       </c>
-      <c r="F15" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="F15" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="7">
         <v>2</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="7">
         <v>1</v>
       </c>
-      <c r="K15" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="L15" s="9" t="s">
+      <c r="K15" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="9" t="s">
+      <c r="M15" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>2003</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="7">
         <v>1</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>2</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G16" s="8" t="s">
+      <c r="F16" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>3</v>
       </c>
-      <c r="I16" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="J16" s="8">
+      <c r="I16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J16" s="7">
         <v>2</v>
       </c>
-      <c r="K16" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="L16" s="9" t="s">
+      <c r="K16" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="M16" s="9" t="s">
+      <c r="M16" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>2004</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="7">
         <v>1</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17" s="7">
         <v>2</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="G17" s="8" t="s">
+      <c r="F17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H17" s="7">
         <v>4</v>
       </c>
-      <c r="I17" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="8">
+      <c r="I17" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="J17" s="7">
         <v>3</v>
       </c>
-      <c r="K17" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="L17" s="9" t="s">
+      <c r="K17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="L17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M17" s="9" t="s">
+      <c r="M17" s="8" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>2005</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="7">
         <v>1</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18" s="7">
         <v>2</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="8" t="s">
+      <c r="F18" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="7">
         <v>5</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="J18" s="8">
+      <c r="I18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="J18" s="7">
         <v>4</v>
       </c>
-      <c r="K18" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="L18" s="9" t="s">
+      <c r="K18" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L18" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="M18" s="9" t="s">
-        <v>78</v>
+      <c r="M18" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>2006</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19" s="7">
         <v>1</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>2</v>
       </c>
-      <c r="F19" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="8" t="s">
+      <c r="F19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G19" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>6</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="J19" s="8">
+      <c r="I19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="J19" s="7">
         <v>5</v>
       </c>
-      <c r="K19" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="L19" s="9" t="s">
+      <c r="K19" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="M19" s="9" t="s">
-        <v>82</v>
+      <c r="M19" s="8" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>2007</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="7">
         <v>1</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20" s="7">
         <v>2</v>
       </c>
-      <c r="F20" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="8" t="s">
+      <c r="F20" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="7">
         <v>7</v>
       </c>
-      <c r="I20" s="8" t="s">
-        <v>84</v>
-      </c>
-      <c r="J20" s="8">
+      <c r="I20" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="7">
         <v>6</v>
       </c>
-      <c r="K20" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="L20" s="9" t="s">
+      <c r="K20" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="L20" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="M20" s="9" t="s">
-        <v>86</v>
+      <c r="M20" s="8" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C21" s="8">
+      <c r="C21" s="7">
         <v>2008</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="7">
         <v>1</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="7">
         <v>2</v>
       </c>
-      <c r="F21" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="G21" s="8" t="s">
+      <c r="F21" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="7">
         <v>8</v>
       </c>
-      <c r="I21" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J21" s="8">
+      <c r="I21" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J21" s="7">
         <v>7</v>
       </c>
-      <c r="K21" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="L21" s="9" t="s">
+      <c r="K21" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="M21" s="9" t="s">
-        <v>90</v>
+      <c r="M21" s="8" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C22" s="8">
+      <c r="C22" s="7">
         <v>3001</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="7">
         <v>1</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22" s="7">
         <v>3</v>
       </c>
-      <c r="F22" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" s="8" t="s">
+      <c r="F22" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="7">
         <v>1</v>
       </c>
-      <c r="I22" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J22" s="8">
+      <c r="I22" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" s="7">
         <v>7</v>
       </c>
-      <c r="K22" s="8" t="s">
+      <c r="K22" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M22" s="9" t="s">
+      <c r="M22" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C23" s="8">
+      <c r="C23" s="7">
         <v>3002</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="7">
         <v>1</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="7">
         <v>3</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="8" t="s">
+      <c r="F23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="7">
         <v>2</v>
       </c>
-      <c r="I23" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J23" s="8">
+      <c r="I23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J23" s="7">
         <v>8</v>
       </c>
-      <c r="K23" s="8" t="s">
+      <c r="K23" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M23" s="9" t="s">
+      <c r="M23" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C24" s="8">
+      <c r="C24" s="7">
         <v>4001</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>2</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="7">
         <v>4</v>
       </c>
-      <c r="F24" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="G24" s="8" t="s">
+      <c r="F24" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="G24" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="7">
         <v>1</v>
       </c>
-      <c r="I24" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J24" s="8">
+      <c r="I24" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="J24" s="7">
         <v>7</v>
       </c>
-      <c r="K24" s="8" t="s">
+      <c r="K24" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="L24" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M24" s="9" t="s">
+      <c r="M24" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C25" s="8">
+      <c r="C25" s="7">
         <v>4002</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="7">
         <v>2</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25" s="7">
         <v>4</v>
       </c>
-      <c r="F25" s="8" t="s">
+      <c r="F25" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="8" t="s">
+      <c r="G25" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H25" s="8">
+      <c r="H25" s="7">
         <v>2</v>
       </c>
-      <c r="I25" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J25" s="8">
+      <c r="I25" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J25" s="7">
         <v>8</v>
       </c>
-      <c r="K25" s="8" t="s">
+      <c r="K25" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M25" s="9" t="s">
+      <c r="M25" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C26" s="8">
+      <c r="C26" s="7">
         <v>5001</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>2</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <v>5</v>
       </c>
-      <c r="F26" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="G26" s="8" t="s">
+      <c r="F26" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="G26" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="7">
         <v>1</v>
       </c>
-      <c r="I26" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J26" s="8">
+      <c r="I26" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="J26" s="7">
         <v>7</v>
       </c>
-      <c r="K26" s="8" t="s">
+      <c r="K26" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M26" s="9" t="s">
+      <c r="M26" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C27" s="8">
+      <c r="C27" s="7">
         <v>5002</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="7">
         <v>2</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27" s="7">
         <v>5</v>
       </c>
-      <c r="F27" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="G27" s="8" t="s">
+      <c r="F27" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H27" s="8">
+      <c r="H27" s="7">
         <v>2</v>
       </c>
-      <c r="I27" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J27" s="8">
+      <c r="I27" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J27" s="7">
         <v>8</v>
       </c>
-      <c r="K27" s="8" t="s">
+      <c r="K27" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="L27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M27" s="9" t="s">
+      <c r="M27" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C28" s="8">
+      <c r="C28" s="7">
         <v>6001</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>2</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <v>6</v>
       </c>
-      <c r="F28" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="G28" s="8" t="s">
+      <c r="F28" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="7">
         <v>1</v>
       </c>
-      <c r="I28" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J28" s="8">
+      <c r="I28" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J28" s="7">
         <v>7</v>
       </c>
-      <c r="K28" s="8" t="s">
+      <c r="K28" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="L28" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M28" s="9" t="s">
+      <c r="M28" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C29" s="8">
+      <c r="C29" s="7">
         <v>6002</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="7">
         <v>2</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29" s="7">
         <v>6</v>
       </c>
-      <c r="F29" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="G29" s="8" t="s">
+      <c r="F29" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="G29" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H29" s="8">
+      <c r="H29" s="7">
         <v>2</v>
       </c>
-      <c r="I29" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J29" s="8">
+      <c r="I29" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="7">
         <v>8</v>
       </c>
-      <c r="K29" s="8" t="s">
+      <c r="K29" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L29" s="9" t="s">
+      <c r="L29" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M29" s="9" t="s">
+      <c r="M29" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C30" s="8">
+      <c r="C30" s="7">
         <v>7001</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>3</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="7">
         <v>7</v>
       </c>
-      <c r="F30" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="8" t="s">
+      <c r="F30" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="7">
         <v>1</v>
       </c>
-      <c r="I30" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J30" s="8">
+      <c r="I30" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="J30" s="7">
         <v>7</v>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="K30" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L30" s="9" t="s">
+      <c r="L30" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M30" s="9" t="s">
+      <c r="M30" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C31" s="8">
+      <c r="C31" s="7">
         <v>7002</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="7">
         <v>3</v>
       </c>
-      <c r="E31" s="8">
+      <c r="E31" s="7">
         <v>7</v>
       </c>
-      <c r="F31" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="G31" s="8" t="s">
+      <c r="F31" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H31" s="8">
+      <c r="H31" s="7">
         <v>2</v>
       </c>
-      <c r="I31" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J31" s="8">
+      <c r="I31" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J31" s="7">
         <v>8</v>
       </c>
-      <c r="K31" s="8" t="s">
+      <c r="K31" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L31" s="9" t="s">
+      <c r="L31" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M31" s="9" t="s">
+      <c r="M31" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C32" s="8">
+      <c r="C32" s="7">
         <v>8001</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>3</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="7">
         <v>8</v>
       </c>
-      <c r="F32" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="G32" s="8" t="s">
+      <c r="F32" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="G32" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="7">
         <v>1</v>
       </c>
-      <c r="I32" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J32" s="8">
+      <c r="I32" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="J32" s="7">
         <v>7</v>
       </c>
-      <c r="K32" s="8" t="s">
+      <c r="K32" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L32" s="9" t="s">
+      <c r="L32" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M32" s="9" t="s">
+      <c r="M32" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C33" s="8">
+      <c r="C33" s="7">
         <v>8002</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="7">
         <v>3</v>
       </c>
-      <c r="E33" s="8">
+      <c r="E33" s="7">
         <v>8</v>
       </c>
-      <c r="F33" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="G33" s="8" t="s">
+      <c r="F33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="G33" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H33" s="8">
+      <c r="H33" s="7">
         <v>2</v>
       </c>
-      <c r="I33" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J33" s="8">
+      <c r="I33" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J33" s="7">
         <v>8</v>
       </c>
-      <c r="K33" s="8" t="s">
+      <c r="K33" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="9" t="s">
+      <c r="L33" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M33" s="9" t="s">
+      <c r="M33" s="8" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C34" s="8">
+      <c r="C34" s="7">
         <v>9001</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>3</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="7">
         <v>9</v>
       </c>
-      <c r="F34" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="G34" s="8" t="s">
+      <c r="F34" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="7">
         <v>1</v>
       </c>
-      <c r="I34" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="J34" s="8">
+      <c r="I34" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="J34" s="7">
         <v>7</v>
       </c>
-      <c r="K34" s="8" t="s">
+      <c r="K34" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="L34" s="9" t="s">
+      <c r="L34" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="M34" s="9" t="s">
+      <c r="M34" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
-      <c r="C35" s="8">
+      <c r="C35" s="7">
         <v>9002</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="7">
         <v>3</v>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="7">
         <v>9</v>
       </c>
-      <c r="F35" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="G35" s="8" t="s">
+      <c r="F35" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="H35" s="8">
+      <c r="H35" s="7">
         <v>2</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="J35" s="8">
+      <c r="I35" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="J35" s="7">
         <v>8</v>
       </c>
-      <c r="K35" s="8" t="s">
+      <c r="K35" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="L35" s="9" t="s">
+      <c r="L35" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="M35" s="9" t="s">
+      <c r="M35" s="8" t="s">
         <v>39</v>
       </c>
     </row>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="110">
   <si>
     <t>c</t>
   </si>
@@ -64,6 +64,9 @@
     <t>开启需要总等级</t>
   </si>
   <si>
+    <t>升级需要经验</t>
+  </si>
+  <si>
     <t>额外属性</t>
   </si>
   <si>
@@ -92,6 +95,9 @@
   </si>
   <si>
     <t>NeedTotalLevel</t>
+  </si>
+  <si>
+    <t>NeedExp</t>
   </si>
   <si>
     <t>AddProperty</t>
@@ -2489,7 +2495,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2">
-    <tableStyle name="MySqlDefault" count="2" xr9:uid="{E5649472-DEE2-4855-B30F-1580C0886754}">
+    <tableStyle name="MySqlDefault" count="2" xr9:uid="{33F73AAB-94A7-4FBD-94B4-D2A5AFC2B6DF}">
       <tableStyleElement type="wholeTable" dxfId="3"/>
       <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
@@ -2532,8 +2538,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:M7" totalsRowShown="0">
-  <tableColumns count="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="C3:N7" totalsRowShown="0">
+  <tableColumns count="12">
     <tableColumn id="1" name="Id">
       <calculatedColumnFormula>C3+1</calculatedColumnFormula>
     </tableColumn>
@@ -2546,6 +2552,7 @@
     </tableColumn>
     <tableColumn id="2" name="开启消耗道具"/>
     <tableColumn id="11" name="开启需要总等级"/>
+    <tableColumn id="12" name="升级需要经验"/>
     <tableColumn id="6" name="额外属性"/>
     <tableColumn id="7" name="额外描述">
       <calculatedColumnFormula>"生命上限提升+"&amp;H4&amp;"%,眩晕抵抗概率+"&amp;H4&amp;"%"</calculatedColumnFormula>
@@ -2841,7 +2848,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:M35"/>
+  <dimension ref="C1:N35"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="4" width="21.625" customWidth="1"/>
@@ -2851,24 +2858,25 @@
     <col min="8" max="8" width="17.375" customWidth="1"/>
     <col min="9" max="9" width="19.75" customWidth="1"/>
     <col min="10" max="10" width="19.5" customWidth="1"/>
-    <col min="11" max="11" width="18" style="1" customWidth="1"/>
-    <col min="12" max="12" width="34" style="1" customWidth="1"/>
-    <col min="13" max="13" width="36.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="19.5" customWidth="1"/>
+    <col min="12" max="12" width="18" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34" style="1" customWidth="1"/>
+    <col min="14" max="14" width="36.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="3:13">
+    <row r="2" ht="20.1" customHeight="1" spans="3:14">
       <c r="G2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>0</v>
-      </c>
       <c r="M2" s="4" t="s">
         <v>0</v>
       </c>
+      <c r="N2" s="4" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="3" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -2893,7 +2901,7 @@
       <c r="J3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="L3" s="6" t="s">
@@ -2902,78 +2910,87 @@
       <c r="M3" s="6" t="s">
         <v>11</v>
       </c>
+      <c r="N3" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="4" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:13">
+    <row r="5" s="2" customFormat="1" ht="19.5" customHeight="1" spans="3:14">
       <c r="C5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="6" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C6" s="7">
         <v>1001</v>
       </c>
@@ -2984,31 +3001,34 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H6" s="7">
         <v>1</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J6" s="7">
         <v>0</v>
       </c>
-      <c r="K6" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>28</v>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M6" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N6" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="7" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C7" s="7">
         <v>1002</v>
       </c>
@@ -3019,31 +3039,34 @@
         <v>1</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H7" s="7">
         <v>2</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7" s="7">
         <v>1</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>33</v>
+      <c r="K7" s="7">
+        <v>10</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="N7" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="8" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C8" s="7">
         <v>1003</v>
       </c>
@@ -3054,31 +3077,34 @@
         <v>1</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H8" s="7">
         <v>3</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J8" s="7">
         <v>2</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>38</v>
+      <c r="K8" s="7">
+        <v>20</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>39</v>
       </c>
       <c r="M8" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="N8" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="9" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C9" s="7">
         <v>1004</v>
       </c>
@@ -3089,31 +3115,34 @@
         <v>1</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H9" s="7">
         <v>4</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J9" s="7">
         <v>3</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>43</v>
+      <c r="K9" s="7">
+        <v>30</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="M9" s="8" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="N9" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
-    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="10" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C10" s="7">
         <v>1005</v>
       </c>
@@ -3124,31 +3153,34 @@
         <v>1</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H10" s="7">
         <v>5</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J10" s="7">
         <v>4</v>
       </c>
-      <c r="K10" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>48</v>
+      <c r="K10" s="7">
+        <v>40</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>49</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="N10" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="11" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C11" s="7">
         <v>1006</v>
       </c>
@@ -3159,31 +3191,34 @@
         <v>1</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H11" s="7">
         <v>6</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J11" s="7">
         <v>5</v>
       </c>
-      <c r="K11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>53</v>
+      <c r="K11" s="7">
+        <v>50</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>54</v>
       </c>
       <c r="M11" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="N11" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="12" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C12" s="7">
         <v>1007</v>
       </c>
@@ -3194,31 +3229,34 @@
         <v>1</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H12" s="7">
         <v>7</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J12" s="7">
         <v>6</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>58</v>
+      <c r="K12" s="7">
+        <v>60</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>59</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="N12" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="13" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C13" s="7">
         <v>1008</v>
       </c>
@@ -3229,31 +3267,34 @@
         <v>1</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H13" s="7">
         <v>8</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J13" s="7">
         <v>7</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>63</v>
+      <c r="K13" s="7">
+        <v>70</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="M13" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="N13" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
-    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="14" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C14" s="7">
         <v>2001</v>
       </c>
@@ -3264,31 +3305,34 @@
         <v>2</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H14" s="7">
         <v>1</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J14" s="7">
         <v>0</v>
       </c>
-      <c r="K14" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>28</v>
+      <c r="K14" s="7">
+        <v>0</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>69</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N14" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="15" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C15" s="7">
         <v>2002</v>
       </c>
@@ -3299,31 +3343,34 @@
         <v>2</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H15" s="7">
         <v>2</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J15" s="7">
         <v>1</v>
       </c>
-      <c r="K15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>33</v>
+      <c r="K15" s="7">
+        <v>10</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="M15" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N15" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="16" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C16" s="7">
         <v>2003</v>
       </c>
@@ -3334,31 +3381,34 @@
         <v>2</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H16" s="7">
         <v>3</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J16" s="7">
         <v>2</v>
       </c>
-      <c r="K16" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>38</v>
+      <c r="K16" s="7">
+        <v>20</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>74</v>
       </c>
       <c r="M16" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
+      </c>
+      <c r="N16" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="17" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C17" s="7">
         <v>2004</v>
       </c>
@@ -3369,31 +3419,34 @@
         <v>2</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H17" s="7">
         <v>4</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="J17" s="7">
         <v>3</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>43</v>
+      <c r="K17" s="7">
+        <v>30</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>77</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>59</v>
+        <v>45</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
-    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="18" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C18" s="7">
         <v>2005</v>
       </c>
@@ -3404,31 +3457,34 @@
         <v>2</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="H18" s="7">
         <v>5</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J18" s="7">
         <v>4</v>
       </c>
-      <c r="K18" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>48</v>
+      <c r="K18" s="7">
+        <v>40</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>80</v>
       </c>
       <c r="M18" s="8" t="s">
-        <v>79</v>
+        <v>50</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>81</v>
       </c>
     </row>
-    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="19" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C19" s="7">
         <v>2006</v>
       </c>
@@ -3439,31 +3495,34 @@
         <v>2</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H19" s="7">
         <v>6</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J19" s="7">
         <v>5</v>
       </c>
-      <c r="K19" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>53</v>
+      <c r="K19" s="7">
+        <v>50</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="M19" s="8" t="s">
-        <v>83</v>
+        <v>55</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>85</v>
       </c>
     </row>
-    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="20" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C20" s="7">
         <v>2007</v>
       </c>
@@ -3474,31 +3533,34 @@
         <v>2</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H20" s="7">
         <v>7</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="J20" s="7">
         <v>6</v>
       </c>
-      <c r="K20" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="L20" s="8" t="s">
-        <v>58</v>
+      <c r="K20" s="7">
+        <v>60</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="M20" s="8" t="s">
-        <v>87</v>
+        <v>60</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>89</v>
       </c>
     </row>
-    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="21" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C21" s="7">
         <v>2008</v>
       </c>
@@ -3509,31 +3571,34 @@
         <v>2</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H21" s="7">
         <v>8</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J21" s="7">
         <v>7</v>
       </c>
-      <c r="K21" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>63</v>
+      <c r="K21" s="7">
+        <v>70</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>92</v>
       </c>
       <c r="M21" s="8" t="s">
-        <v>91</v>
+        <v>65</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>93</v>
       </c>
     </row>
-    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="22" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C22" s="7">
         <v>3001</v>
       </c>
@@ -3544,31 +3609,34 @@
         <v>3</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H22" s="7">
         <v>1</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J22" s="7">
         <v>7</v>
       </c>
-      <c r="K22" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>28</v>
+      <c r="K22" s="7">
+        <v>80</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="23" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C23" s="7">
         <v>3002</v>
       </c>
@@ -3579,31 +3647,34 @@
         <v>3</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23" s="7">
         <v>2</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J23" s="7">
         <v>8</v>
       </c>
-      <c r="K23" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>33</v>
+      <c r="K23" s="7">
+        <v>90</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M23" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C24" s="7">
         <v>4001</v>
       </c>
@@ -3614,31 +3685,34 @@
         <v>4</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H24" s="7">
         <v>1</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="J24" s="7">
         <v>7</v>
       </c>
-      <c r="K24" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>28</v>
+      <c r="K24" s="7">
+        <v>100</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M24" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="25" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C25" s="7">
         <v>4002</v>
       </c>
@@ -3649,31 +3723,34 @@
         <v>4</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H25" s="7">
         <v>2</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J25" s="7">
         <v>8</v>
       </c>
-      <c r="K25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L25" s="8" t="s">
-        <v>33</v>
+      <c r="K25" s="7">
+        <v>110</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M25" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="26" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C26" s="7">
         <v>5001</v>
       </c>
@@ -3684,31 +3761,34 @@
         <v>5</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H26" s="7">
         <v>1</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J26" s="7">
         <v>7</v>
       </c>
-      <c r="K26" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="8" t="s">
-        <v>28</v>
+      <c r="K26" s="7">
+        <v>120</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="27" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C27" s="7">
         <v>5002</v>
       </c>
@@ -3719,31 +3799,34 @@
         <v>5</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H27" s="7">
         <v>2</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J27" s="7">
         <v>8</v>
       </c>
-      <c r="K27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>33</v>
+      <c r="K27" s="7">
+        <v>130</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M27" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="28" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C28" s="7">
         <v>6001</v>
       </c>
@@ -3754,31 +3837,34 @@
         <v>6</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H28" s="7">
         <v>1</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J28" s="7">
         <v>7</v>
       </c>
-      <c r="K28" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="8" t="s">
-        <v>28</v>
+      <c r="K28" s="7">
+        <v>140</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M28" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="29" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C29" s="7">
         <v>6002</v>
       </c>
@@ -3789,31 +3875,34 @@
         <v>6</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H29" s="7">
         <v>2</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J29" s="7">
         <v>8</v>
       </c>
-      <c r="K29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>33</v>
+      <c r="K29" s="7">
+        <v>150</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M29" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="30" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C30" s="7">
         <v>7001</v>
       </c>
@@ -3824,31 +3913,34 @@
         <v>7</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H30" s="7">
         <v>1</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J30" s="7">
         <v>7</v>
       </c>
-      <c r="K30" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" s="8" t="s">
-        <v>28</v>
+      <c r="K30" s="7">
+        <v>160</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M30" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N30" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="31" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C31" s="7">
         <v>7002</v>
       </c>
@@ -3859,31 +3951,34 @@
         <v>7</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H31" s="7">
         <v>2</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J31" s="7">
         <v>8</v>
       </c>
-      <c r="K31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>33</v>
+      <c r="K31" s="7">
+        <v>170</v>
+      </c>
+      <c r="L31" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M31" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N31" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="32" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C32" s="7">
         <v>8001</v>
       </c>
@@ -3894,31 +3989,34 @@
         <v>8</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H32" s="7">
         <v>1</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="J32" s="7">
         <v>7</v>
       </c>
-      <c r="K32" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>28</v>
+      <c r="K32" s="7">
+        <v>180</v>
+      </c>
+      <c r="L32" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M32" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N32" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="33" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C33" s="7">
         <v>8002</v>
       </c>
@@ -3929,31 +4027,34 @@
         <v>8</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H33" s="7">
         <v>2</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J33" s="7">
         <v>8</v>
       </c>
-      <c r="K33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>33</v>
+      <c r="K33" s="7">
+        <v>190</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M33" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N33" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="34" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C34" s="7">
         <v>9001</v>
       </c>
@@ -3964,31 +4065,34 @@
         <v>9</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H34" s="7">
         <v>1</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J34" s="7">
         <v>7</v>
       </c>
-      <c r="K34" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="8" t="s">
-        <v>28</v>
+      <c r="K34" s="7">
+        <v>200</v>
+      </c>
+      <c r="L34" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="M34" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="N34" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:13">
+    <row r="35" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:14">
       <c r="C35" s="7">
         <v>9002</v>
       </c>
@@ -3999,28 +4103,31 @@
         <v>9</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H35" s="7">
         <v>2</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J35" s="7">
         <v>8</v>
       </c>
-      <c r="K35" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="L35" s="8" t="s">
-        <v>33</v>
+      <c r="K35" s="7">
+        <v>210</v>
+      </c>
+      <c r="L35" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="M35" s="8" t="s">
-        <v>39</v>
+        <v>35</v>
+      </c>
+      <c r="N35" s="8" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -85,7 +85,7 @@
     <t>MagicName</t>
   </si>
   <si>
-    <t>ShieldName_EN</t>
+    <t>MagicName_EN</t>
   </si>
   <si>
     <t>MagicLevel</t>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E54B33A-34D9-48D4-82A3-7475B69E24EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854C9324-9217-40F1-B4CC-A33B64F0C165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="274">
   <si>
     <t>c</t>
   </si>
@@ -106,166 +106,773 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 1</t>
-  </si>
-  <si>
-    <t>205703;0.01</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害1%</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 1%.</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 2</t>
-  </si>
-  <si>
-    <t>205703;0.02</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害2%</t>
-  </si>
-  <si>
-    <t>Reduce damage from player's normal attacks by 2%</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 3</t>
-  </si>
-  <si>
-    <t>205703;0.03</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害3%</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 2%.</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 4</t>
-  </si>
-  <si>
-    <t>205703;0.04</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害4%</t>
-  </si>
-  <si>
-    <t>Reduce damage from player's normal attacks by 3%</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 5</t>
-  </si>
-  <si>
-    <t>205703;0.05</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害5%</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 3%.</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 6</t>
-  </si>
-  <si>
-    <t>205703;0.06</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害6%</t>
-  </si>
-  <si>
-    <t>Reduce damage from player's normal attacks by 4%</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 7</t>
-  </si>
-  <si>
-    <t>205703;0.07</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害7%</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 4%.</t>
-  </si>
-  <si>
-    <t>Lava Soul Level 8</t>
-  </si>
-  <si>
-    <t>205703;0.08</t>
-  </si>
-  <si>
-    <t>降低受到玩家普通攻击伤害8%</t>
-  </si>
-  <si>
-    <t>Reduce damage from player's normal attacks by 5%</t>
-  </si>
-  <si>
-    <t>205803;0.01</t>
-  </si>
-  <si>
-    <t>205803;0.02</t>
-  </si>
-  <si>
-    <t>205803;0.03</t>
-  </si>
-  <si>
-    <t>205803;0.04</t>
-  </si>
-  <si>
-    <t>205803;0.05</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 5%.</t>
-  </si>
-  <si>
-    <t>205803;0.06</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 6%.</t>
-  </si>
-  <si>
-    <t>205803;0.07</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 7%.</t>
-  </si>
-  <si>
-    <t>205803;0.08</t>
-  </si>
-  <si>
-    <t>Reduces damage taken from player basic attacks by 8%.</t>
-  </si>
-  <si>
-    <t>1;1000000</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000180;10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;10000000@10000180;10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>10000181;1</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>魔能攻击孔位</t>
+    <t>1;30000000@10000180;1500</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>魔能防护孔位</t>
+    <t>1;5000000@10000180;300</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>全能孔位</t>
+    <t>1;20000000@10000180;1000</t>
     <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;50000000@10000180;2000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;10000000@10000180;600</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1;3000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;100@1;1000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;150@1;2000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;200@1;3000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;300@1;4000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;450@1;5000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;600@1;6000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;800@1;7000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;1000@1;8500000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000180;1200@1;10000000</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1级攻击栏位</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2级攻击栏位</t>
+  </si>
+  <si>
+    <t>3级攻击栏位</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>4级攻击栏位</t>
+  </si>
+  <si>
+    <t>5级攻击栏位</t>
+  </si>
+  <si>
+    <t>6级攻击栏位</t>
+  </si>
+  <si>
+    <t>7级攻击栏位</t>
+  </si>
+  <si>
+    <t>8级攻击栏位</t>
+  </si>
+  <si>
+    <t>9级攻击栏位</t>
+  </si>
+  <si>
+    <t>10级攻击栏位</t>
+  </si>
+  <si>
+    <t>1级防护栏位</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2级防护栏位</t>
+  </si>
+  <si>
+    <t>3级防护栏位</t>
+  </si>
+  <si>
+    <t>4级防护栏位</t>
+  </si>
+  <si>
+    <t>5级防护栏位</t>
+  </si>
+  <si>
+    <t>6级防护栏位</t>
+  </si>
+  <si>
+    <t>7级防护栏位</t>
+  </si>
+  <si>
+    <t>8级防护栏位</t>
+  </si>
+  <si>
+    <t>9级防护栏位</t>
+  </si>
+  <si>
+    <t>10级防护栏位</t>
+  </si>
+  <si>
+    <t>1级全能栏位</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>2级全能栏位</t>
+  </si>
+  <si>
+    <t>3级全能栏位</t>
+  </si>
+  <si>
+    <t>4级全能栏位</t>
+  </si>
+  <si>
+    <t>5级全能栏位</t>
+  </si>
+  <si>
+    <t>6级全能栏位</t>
+  </si>
+  <si>
+    <t>7级全能栏位</t>
+  </si>
+  <si>
+    <t>8级全能栏位</t>
+  </si>
+  <si>
+    <t>9级全能栏位</t>
+  </si>
+  <si>
+    <t>10级全能栏位</t>
+  </si>
+  <si>
+    <t>Level 1 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 2 Attack Slot</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level 3 Attack Slot</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level 4 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 5 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 6 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 7 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 8 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 9 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 10 Attack Slot</t>
+  </si>
+  <si>
+    <t>Level 1 Defense Slot</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Level 2 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 3 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 4 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 5 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 6 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 7 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 8 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 9 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 10 Defense Slot</t>
+  </si>
+  <si>
+    <t>Level 1 All-Round Slot</t>
+  </si>
+  <si>
+    <t>100403;10@100603;10</t>
+  </si>
+  <si>
+    <t>100403;25@100603;25</t>
+  </si>
+  <si>
+    <t>100403;40@100603;40</t>
+  </si>
+  <si>
+    <t>100403;60@100603;60</t>
+  </si>
+  <si>
+    <t>100403;90@100603;90</t>
+  </si>
+  <si>
+    <t>100403;120@100603;120</t>
+  </si>
+  <si>
+    <t>100403;150@100603;150</t>
+  </si>
+  <si>
+    <t>100403;180@100603;180</t>
+  </si>
+  <si>
+    <t>100403;210@100603;210</t>
+  </si>
+  <si>
+    <t>100403;240@100603;240</t>
+  </si>
+  <si>
+    <t>100403;10@100803;10</t>
+  </si>
+  <si>
+    <t>100403;25@100803;25</t>
+  </si>
+  <si>
+    <t>100403;40@100803;40</t>
+  </si>
+  <si>
+    <t>100403;60@100803;60</t>
+  </si>
+  <si>
+    <t>100403;90@100803;90</t>
+  </si>
+  <si>
+    <t>100403;120@100803;120</t>
+  </si>
+  <si>
+    <t>100403;150@100803;150</t>
+  </si>
+  <si>
+    <t>100403;180@100803;180</t>
+  </si>
+  <si>
+    <t>100403;210@100803;210</t>
+  </si>
+  <si>
+    <t>100403;240@100803;240</t>
+  </si>
+  <si>
+    <t>100403;10@100203;25</t>
+  </si>
+  <si>
+    <t>100403;25@100203;62.5</t>
+  </si>
+  <si>
+    <t>100403;40@100203;100</t>
+  </si>
+  <si>
+    <t>100403;60@100203;150</t>
+  </si>
+  <si>
+    <t>100403;90@100203;225</t>
+  </si>
+  <si>
+    <t>100403;120@100203;300</t>
+  </si>
+  <si>
+    <t>100403;150@100203;375</t>
+  </si>
+  <si>
+    <t>100403;180@100203;450</t>
+  </si>
+  <si>
+    <t>100403;210@100203;525</t>
+  </si>
+  <si>
+    <t>100403;240@100203;600</t>
+  </si>
+  <si>
+    <t>100203;50</t>
+  </si>
+  <si>
+    <t>100203;125</t>
+  </si>
+  <si>
+    <t>100203;200</t>
+  </si>
+  <si>
+    <t>100203;300</t>
+  </si>
+  <si>
+    <t>100203;450</t>
+  </si>
+  <si>
+    <t>100203;600</t>
+  </si>
+  <si>
+    <t>100203;750</t>
+  </si>
+  <si>
+    <t>100203;900</t>
+  </si>
+  <si>
+    <t>100203;1050</t>
+  </si>
+  <si>
+    <t>100203;1200</t>
+  </si>
+  <si>
+    <t>101003;10@100203;25</t>
+  </si>
+  <si>
+    <t>101003;25@100203;60</t>
+  </si>
+  <si>
+    <t>101003;40@100203;100</t>
+  </si>
+  <si>
+    <t>101003;60@100203;150</t>
+  </si>
+  <si>
+    <t>101003;90@100203;225</t>
+  </si>
+  <si>
+    <t>101003;120@100203;300</t>
+  </si>
+  <si>
+    <t>101003;150@100203;375</t>
+  </si>
+  <si>
+    <t>101003;180@100203;450</t>
+  </si>
+  <si>
+    <t>101003;210@100203;525</t>
+  </si>
+  <si>
+    <t>101003;240@100203;600</t>
+  </si>
+  <si>
+    <t>100403;25@100203;60</t>
+  </si>
+  <si>
+    <t>100203;25@100603;5@100803;5</t>
+  </si>
+  <si>
+    <t>100203;60@100603;10@100803;10</t>
+  </si>
+  <si>
+    <t>100203;100@100603;15@100803;15</t>
+  </si>
+  <si>
+    <t>100203;150@100603;20@100803;20</t>
+  </si>
+  <si>
+    <t>100203;225@100603;30@100803;30</t>
+  </si>
+  <si>
+    <t>100203;300@100603;40@100803;40</t>
+  </si>
+  <si>
+    <t>100203;375@100603;50@100803;50</t>
+  </si>
+  <si>
+    <t>100203;450@100603;60@100803;60</t>
+  </si>
+  <si>
+    <t>100203;525@100603;70@100803;70</t>
+  </si>
+  <si>
+    <t>100203;600@100603;80@100803;80</t>
+  </si>
+  <si>
+    <t>攻击提升10点;物防提升10点</t>
+  </si>
+  <si>
+    <t>攻击提升25点;物防提升25点</t>
+  </si>
+  <si>
+    <t>攻击提升40点;物防提升40点</t>
+  </si>
+  <si>
+    <t>攻击提升60点;物防提升60点</t>
+  </si>
+  <si>
+    <t>攻击提升90点;物防提升90点</t>
+  </si>
+  <si>
+    <t>攻击提升120点;物防提升120点</t>
+  </si>
+  <si>
+    <t>攻击提升150点;物防提升150点</t>
+  </si>
+  <si>
+    <t>攻击提升180点;物防提升180点</t>
+  </si>
+  <si>
+    <t>攻击提升210点;物防提升210点</t>
+  </si>
+  <si>
+    <t>攻击提升240点;物防提升240点</t>
+  </si>
+  <si>
+    <t>攻击提升10点;魔防提升10点</t>
+  </si>
+  <si>
+    <t>攻击提升25点;魔防提升25点</t>
+  </si>
+  <si>
+    <t>攻击提升40点;魔防提升40点</t>
+  </si>
+  <si>
+    <t>攻击提升60点;魔防提升60点</t>
+  </si>
+  <si>
+    <t>攻击提升90点;魔防提升90点</t>
+  </si>
+  <si>
+    <t>攻击提升120点;魔防提升120点</t>
+  </si>
+  <si>
+    <t>攻击提升150点;魔防提升150点</t>
+  </si>
+  <si>
+    <t>攻击提升180点;魔防提升180点</t>
+  </si>
+  <si>
+    <t>攻击提升210点;魔防提升210点</t>
+  </si>
+  <si>
+    <t>攻击提升240点;魔防提升240点</t>
+  </si>
+  <si>
+    <t>攻击提升10点;血量提升25点</t>
+  </si>
+  <si>
+    <t>攻击提升25点;血量提升60点</t>
+  </si>
+  <si>
+    <t>攻击提升40点;血量提升100点</t>
+  </si>
+  <si>
+    <t>攻击提升60点;血量提升150点</t>
+  </si>
+  <si>
+    <t>攻击提升90点;血量提升225点</t>
+  </si>
+  <si>
+    <t>攻击提升120点;血量提升300点</t>
+  </si>
+  <si>
+    <t>攻击提升150点;血量提升375点</t>
+  </si>
+  <si>
+    <t>攻击提升180点;血量提升450点</t>
+  </si>
+  <si>
+    <t>攻击提升210点;血量提升525点</t>
+  </si>
+  <si>
+    <t>攻击提升240点;血量提升600点</t>
+  </si>
+  <si>
+    <t>血量提升50点</t>
+  </si>
+  <si>
+    <t>血量提升125点</t>
+  </si>
+  <si>
+    <t>血量提升200点</t>
+  </si>
+  <si>
+    <t>血量提升300点</t>
+  </si>
+  <si>
+    <t>血量提升450点</t>
+  </si>
+  <si>
+    <t>血量提升600点</t>
+  </si>
+  <si>
+    <t>血量提升750点</t>
+  </si>
+  <si>
+    <t>血量提升900点</t>
+  </si>
+  <si>
+    <t>血量提升1050点</t>
+  </si>
+  <si>
+    <t>血量提升1200点</t>
+  </si>
+  <si>
+    <t>魔法提升10点;血量提升25点</t>
+  </si>
+  <si>
+    <t>魔法提升25点;血量提升60点</t>
+  </si>
+  <si>
+    <t>魔法提升40点;血量提升100点</t>
+  </si>
+  <si>
+    <t>魔法提升60点;血量提升150点</t>
+  </si>
+  <si>
+    <t>魔法提升90点;血量提升225点</t>
+  </si>
+  <si>
+    <t>魔法提升120点;血量提升300点</t>
+  </si>
+  <si>
+    <t>魔法提升150点;血量提升375点</t>
+  </si>
+  <si>
+    <t>魔法提升180点;血量提升450点</t>
+  </si>
+  <si>
+    <t>魔法提升210点;血量提升525点</t>
+  </si>
+  <si>
+    <t>魔法提升240点;血量提升600点</t>
+  </si>
+  <si>
+    <t>血量提升25点;物防提升5点点;魔防提升5点</t>
+  </si>
+  <si>
+    <t>血量提升60点;物防提升10点点;魔防提升10点</t>
+  </si>
+  <si>
+    <t>血量提升100点;物防提升15点点;魔防提升15点</t>
+  </si>
+  <si>
+    <t>血量提升150点;物防提升20点点;魔防提升20点</t>
+  </si>
+  <si>
+    <t>血量提升225点;物防提升30点点;魔防提升30点</t>
+  </si>
+  <si>
+    <t>血量提升300点;物防提升40点点;魔防提升40点</t>
+  </si>
+  <si>
+    <t>血量提升375点;物防提升50点点;魔防提升50点</t>
+  </si>
+  <si>
+    <t>血量提升450点;物防提升60点点;魔防提升60点</t>
+  </si>
+  <si>
+    <t>血量提升525点;物防提升70点点;魔防提升70点</t>
+  </si>
+  <si>
+    <t>血量提升600点;物防提升80点点;魔防提升80点</t>
+  </si>
+  <si>
+    <t>Attack +10; Physical Defense +10</t>
+  </si>
+  <si>
+    <t>Attack +25; Physical Defense +25</t>
+  </si>
+  <si>
+    <t>Attack +40; Physical Defense +40</t>
+  </si>
+  <si>
+    <t>Attack +60; Physical Defense +60</t>
+  </si>
+  <si>
+    <t>Attack +90; Physical Defense +90</t>
+  </si>
+  <si>
+    <t>Attack +120; Physical Defense +120</t>
+  </si>
+  <si>
+    <t>Attack +150; Physical Defense +150</t>
+  </si>
+  <si>
+    <t>Attack +180; Physical Defense +180</t>
+  </si>
+  <si>
+    <t>Attack +210; Physical Defense +210</t>
+  </si>
+  <si>
+    <t>Attack +240; Physical Defense +240</t>
+  </si>
+  <si>
+    <t>Attack +10; Magical Defense +10</t>
+  </si>
+  <si>
+    <t>Attack +25; Magical Defense +25</t>
+  </si>
+  <si>
+    <t>Attack +40; Magical Defense +40</t>
+  </si>
+  <si>
+    <t>Attack +60; Magical Defense +60</t>
+  </si>
+  <si>
+    <t>Attack +90; Magical Defense +90</t>
+  </si>
+  <si>
+    <t>Attack +120; Magical Defense +120</t>
+  </si>
+  <si>
+    <t>Attack +150; Magical Defense +150</t>
+  </si>
+  <si>
+    <t>Attack +180; Magical Defense +180</t>
+  </si>
+  <si>
+    <t>Attack +210; Magical Defense +210</t>
+  </si>
+  <si>
+    <t>Attack +240; Magical Defense +240</t>
+  </si>
+  <si>
+    <t>Attack +10; HP +25</t>
+  </si>
+  <si>
+    <t>Attack +25; HP +60</t>
+  </si>
+  <si>
+    <t>Attack +40; HP +100</t>
+  </si>
+  <si>
+    <t>Attack +60; HP +150</t>
+  </si>
+  <si>
+    <t>Attack +90; HP +225</t>
+  </si>
+  <si>
+    <t>Attack +120; HP +300</t>
+  </si>
+  <si>
+    <t>Attack +150; HP +375</t>
+  </si>
+  <si>
+    <t>Attack +180; HP +450</t>
+  </si>
+  <si>
+    <t>Attack +210; HP +525</t>
+  </si>
+  <si>
+    <t>Attack +240; HP +600</t>
+  </si>
+  <si>
+    <t>HP +50</t>
+  </si>
+  <si>
+    <t>HP +125</t>
+  </si>
+  <si>
+    <t>HP +200</t>
+  </si>
+  <si>
+    <t>HP +300</t>
+  </si>
+  <si>
+    <t>HP +450</t>
+  </si>
+  <si>
+    <t>HP +600</t>
+  </si>
+  <si>
+    <t>HP +750</t>
+  </si>
+  <si>
+    <t>HP +900</t>
+  </si>
+  <si>
+    <t>HP +1050</t>
+  </si>
+  <si>
+    <t>HP +1200</t>
+  </si>
+  <si>
+    <t>Magic +10; HP +25</t>
+  </si>
+  <si>
+    <t>Magic +25; HP +60</t>
+  </si>
+  <si>
+    <t>Magic +40; HP +100</t>
+  </si>
+  <si>
+    <t>Magic +60; HP +150</t>
+  </si>
+  <si>
+    <t>Magic +90; HP +225</t>
+  </si>
+  <si>
+    <t>Magic +120; HP +300</t>
+  </si>
+  <si>
+    <t>Magic +150; HP +375</t>
+  </si>
+  <si>
+    <t>Magic +180; HP +450</t>
+  </si>
+  <si>
+    <t>Magic +210; HP +525</t>
+  </si>
+  <si>
+    <t>Magic +240; HP +600</t>
+  </si>
+  <si>
+    <t>HP +25; Physical Defense +5; Magical Defense +5</t>
+  </si>
+  <si>
+    <t>HP +60; Physical Defense +10; Magical Defense +10</t>
+  </si>
+  <si>
+    <t>HP +100; Physical Defense +15; Magical Defense +15</t>
+  </si>
+  <si>
+    <t>HP +150; Physical Defense +20; Magical Defense +20</t>
+  </si>
+  <si>
+    <t>HP +225; Physical Defense +30; Magical Defense +30</t>
+  </si>
+  <si>
+    <t>HP +300; Physical Defense +40; Magical Defense +40</t>
+  </si>
+  <si>
+    <t>HP +375; Physical Defense +50; Magical Defense +50</t>
+  </si>
+  <si>
+    <t>HP +450; Physical Defense +60; Magical Defense +60</t>
+  </si>
+  <si>
+    <t>HP +525; Physical Defense +70; Magical Defense +70</t>
+  </si>
+  <si>
+    <t>HP +600; Physical Defense +80; Magical Defense +80</t>
   </si>
 </sst>
 </file>
@@ -1447,7 +2054,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1470,6 +2077,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="313">
@@ -1908,7 +2518,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C3:N7" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="表1" displayName="表1" ref="C3:N5" totalsRowShown="0">
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id">
       <calculatedColumnFormula>C3+1</calculatedColumnFormula>
@@ -2218,7 +2828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:N35"/>
+  <dimension ref="A1:N95"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="4" width="21.625" customWidth="1"/>
@@ -2226,7 +2836,7 @@
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="19.875" customWidth="1"/>
     <col min="8" max="8" width="17.375" customWidth="1"/>
-    <col min="9" max="9" width="19.75" customWidth="1"/>
+    <col min="9" max="9" width="23.875" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="19.5" customWidth="1"/>
     <col min="12" max="12" width="18" style="1" customWidth="1"/>
     <col min="13" max="13" width="34" style="1" customWidth="1"/>
@@ -2370,31 +2980,31 @@
         <v>1</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="H6" s="6">
         <v>1</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="J6" s="6">
         <v>0</v>
       </c>
       <c r="K6" s="6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>28</v>
+        <v>154</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>29</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2408,31 +3018,31 @@
         <v>1</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="H7" s="6">
         <v>2</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="J7" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="6">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>33</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2446,31 +3056,31 @@
         <v>1</v>
       </c>
       <c r="F8" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>74</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>34</v>
       </c>
       <c r="H8" s="6">
         <v>3</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>71</v>
+        <v>34</v>
       </c>
       <c r="J8" s="6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K8" s="6">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>37</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2484,31 +3094,31 @@
         <v>1</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="H9" s="6">
         <v>4</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="J9" s="6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K9" s="6">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>40</v>
+        <v>157</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>41</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2522,31 +3132,31 @@
         <v>1</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>42</v>
+        <v>76</v>
       </c>
       <c r="H10" s="6">
         <v>5</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="J10" s="6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K10" s="6">
-        <v>40</v>
+        <v>450</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>43</v>
+        <v>97</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>44</v>
+        <v>158</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>45</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2560,31 +3170,31 @@
         <v>1</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="H11" s="6">
         <v>6</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="J11" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="6">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>48</v>
+        <v>159</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>49</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2598,31 +3208,31 @@
         <v>1</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="H12" s="6">
         <v>7</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="J12" s="6">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K12" s="6">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>51</v>
+        <v>99</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>52</v>
+        <v>160</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>53</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -2636,112 +3246,112 @@
         <v>1</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="H13" s="6">
         <v>8</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="J13" s="6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K13" s="6">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>56</v>
+        <v>161</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>57</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C14" s="6">
-        <v>2001</v>
+        <v>1009</v>
       </c>
       <c r="D14" s="6">
         <v>1</v>
       </c>
       <c r="E14" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="H14" s="6">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="J14" s="6">
         <v>0</v>
       </c>
       <c r="K14" s="6">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>28</v>
+        <v>162</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>29</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C15" s="6">
-        <v>2002</v>
+        <v>1010</v>
       </c>
       <c r="D15" s="6">
         <v>1</v>
       </c>
       <c r="E15" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="H15" s="6">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="J15" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="6">
-        <v>10</v>
+        <v>1500</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>59</v>
+        <v>102</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>37</v>
+        <v>223</v>
       </c>
     </row>
     <row r="16" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C16" s="6">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="D16" s="6">
         <v>1</v>
@@ -2749,37 +3359,37 @@
       <c r="E16" s="6">
         <v>2</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>74</v>
+      <c r="F16" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="H16" s="6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>71</v>
+        <v>31</v>
       </c>
       <c r="J16" s="6">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K16" s="6">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>60</v>
+        <v>103</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>36</v>
+        <v>164</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C17" s="6">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D17" s="6">
         <v>1</v>
@@ -2787,37 +3397,37 @@
       <c r="E17" s="6">
         <v>2</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>74</v>
+      <c r="F17" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="H17" s="6">
-        <v>4</v>
-      </c>
-      <c r="I17" s="8" t="s">
-        <v>71</v>
+        <v>2</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="J17" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K17" s="6">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>61</v>
+        <v>104</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>40</v>
+        <v>165</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C18" s="6">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="D18" s="6">
         <v>1</v>
@@ -2826,36 +3436,36 @@
         <v>2</v>
       </c>
       <c r="F18" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="G18" s="6" t="s">
-        <v>38</v>
-      </c>
       <c r="H18" s="6">
+        <v>3</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="6">
         <v>5</v>
       </c>
-      <c r="I18" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J18" s="6">
-        <v>4</v>
-      </c>
       <c r="K18" s="6">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>44</v>
+        <v>166</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="6">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -2864,36 +3474,36 @@
         <v>2</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="H19" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="J19" s="6">
         <v>5</v>
       </c>
       <c r="K19" s="6">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>48</v>
+        <v>167</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C20" s="6">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="D20" s="6">
         <v>1</v>
@@ -2902,36 +3512,36 @@
         <v>2</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="J20" s="6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K20" s="6">
-        <v>60</v>
+        <v>450</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>52</v>
+        <v>168</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C21" s="6">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -2940,563 +3550,2847 @@
         <v>2</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="H21" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="J21" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K21" s="6">
-        <v>70</v>
+        <v>600</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>68</v>
+        <v>108</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>56</v>
+        <v>169</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="22" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C22" s="6">
-        <v>3001</v>
+        <v>2007</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
       </c>
       <c r="E22" s="6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="H22" s="6">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>72</v>
+        <v>38</v>
       </c>
       <c r="J22" s="6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K22" s="6">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C23" s="6">
-        <v>3002</v>
+        <v>2008</v>
       </c>
       <c r="D23" s="6">
         <v>1</v>
       </c>
       <c r="E23" s="6">
+        <v>2</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H23" s="6">
+        <v>8</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J23" s="6">
+        <v>5</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C24" s="6">
+        <v>2009</v>
+      </c>
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H24" s="6">
+        <v>9</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J24" s="6">
+        <v>5</v>
+      </c>
+      <c r="K24" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C25" s="6">
+        <v>2010</v>
+      </c>
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
+        <v>2</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H25" s="6">
+        <v>10</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J25" s="6">
+        <v>5</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C26" s="6">
+        <v>3001</v>
+      </c>
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6">
         <v>3</v>
       </c>
-      <c r="F23" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="6">
-        <v>2</v>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J23" s="6">
-        <v>8</v>
-      </c>
-      <c r="K23" s="6">
-        <v>90</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M23" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="24" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C24" s="6">
-        <v>4001</v>
-      </c>
-      <c r="D24" s="6">
-        <v>2</v>
-      </c>
-      <c r="E24" s="6">
-        <v>4</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H24" s="6">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8" t="s">
+      <c r="F26" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="J24" s="6">
-        <v>7</v>
-      </c>
-      <c r="K24" s="6">
-        <v>100</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M24" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C25" s="6">
-        <v>4002</v>
-      </c>
-      <c r="D25" s="6">
-        <v>2</v>
-      </c>
-      <c r="E25" s="6">
-        <v>4</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="6">
-        <v>2</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J25" s="6">
-        <v>8</v>
-      </c>
-      <c r="K25" s="6">
-        <v>110</v>
-      </c>
-      <c r="L25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N25" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="26" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C26" s="6">
-        <v>5001</v>
-      </c>
-      <c r="D26" s="6">
-        <v>2</v>
-      </c>
-      <c r="E26" s="6">
-        <v>5</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>26</v>
       </c>
       <c r="H26" s="6">
         <v>1</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="J26" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K26" s="6">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>28</v>
+        <v>174</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="6">
-        <v>5002</v>
+        <v>3002</v>
       </c>
       <c r="D27" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E27" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="H27" s="6">
         <v>2</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="I27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" s="6">
+        <v>12</v>
+      </c>
+      <c r="K27" s="6">
+        <v>150</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C28" s="6">
+        <v>3003</v>
+      </c>
+      <c r="D28" s="6">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6">
+        <v>3</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="H28" s="6">
+        <v>3</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J28" s="6">
+        <v>12</v>
+      </c>
+      <c r="K28" s="6">
+        <v>200</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A29" s="9"/>
+      <c r="C29" s="6">
+        <v>3004</v>
+      </c>
+      <c r="D29" s="6">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H29" s="6">
+        <v>4</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J29" s="6">
+        <v>12</v>
+      </c>
+      <c r="K29" s="6">
+        <v>300</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C30" s="6">
+        <v>3005</v>
+      </c>
+      <c r="D30" s="6">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>3</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="6">
+        <v>5</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="6">
+        <v>12</v>
+      </c>
+      <c r="K30" s="6">
+        <v>450</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="M30" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A31" s="9"/>
+      <c r="C31" s="6">
+        <v>3006</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>3</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="6">
+        <v>6</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J31" s="6">
+        <v>12</v>
+      </c>
+      <c r="K31" s="6">
+        <v>600</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M31" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C32" s="6">
+        <v>3007</v>
+      </c>
+      <c r="D32" s="6">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6">
+        <v>3</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="H32" s="6">
+        <v>7</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J32" s="6">
+        <v>12</v>
+      </c>
+      <c r="K32" s="6">
+        <v>800</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M32" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="9"/>
+      <c r="C33" s="6">
+        <v>3008</v>
+      </c>
+      <c r="D33" s="6">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6">
+        <v>3</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="H33" s="6">
+        <v>8</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J33" s="6">
+        <v>12</v>
+      </c>
+      <c r="K33" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M33" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C34" s="6">
+        <v>3009</v>
+      </c>
+      <c r="D34" s="6">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6">
+        <v>3</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H34" s="6">
+        <v>9</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J34" s="6">
+        <v>12</v>
+      </c>
+      <c r="K34" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="9"/>
+      <c r="C35" s="6">
+        <v>3010</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6">
+        <v>3</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="H35" s="6">
+        <v>10</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J35" s="6">
+        <v>12</v>
+      </c>
+      <c r="K35" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M35" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C36" s="6">
+        <v>4001</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2</v>
+      </c>
+      <c r="E36" s="6">
+        <v>4</v>
+      </c>
+      <c r="F36" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" s="6">
+        <v>18</v>
+      </c>
+      <c r="K36" s="6">
+        <v>100</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="M36" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C37" s="6">
+        <v>4002</v>
+      </c>
+      <c r="D37" s="6">
+        <v>2</v>
+      </c>
+      <c r="E37" s="6">
+        <v>4</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H37" s="6">
+        <v>2</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J37" s="6">
+        <v>18</v>
+      </c>
+      <c r="K37" s="6">
+        <v>150</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M37" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C38" s="6">
+        <v>4003</v>
+      </c>
+      <c r="D38" s="6">
+        <v>2</v>
+      </c>
+      <c r="E38" s="6">
+        <v>4</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="6">
+        <v>3</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J38" s="6">
+        <v>18</v>
+      </c>
+      <c r="K38" s="6">
+        <v>200</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="M38" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C39" s="6">
+        <v>4004</v>
+      </c>
+      <c r="D39" s="6">
+        <v>2</v>
+      </c>
+      <c r="E39" s="6">
+        <v>4</v>
+      </c>
+      <c r="F39" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" s="6">
+        <v>4</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J39" s="6">
+        <v>18</v>
+      </c>
+      <c r="K39" s="6">
+        <v>300</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="M39" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C40" s="6">
+        <v>4005</v>
+      </c>
+      <c r="D40" s="6">
+        <v>2</v>
+      </c>
+      <c r="E40" s="6">
+        <v>4</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H40" s="6">
+        <v>5</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J40" s="6">
+        <v>18</v>
+      </c>
+      <c r="K40" s="6">
+        <v>450</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M40" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C41" s="6">
+        <v>4006</v>
+      </c>
+      <c r="D41" s="6">
+        <v>2</v>
+      </c>
+      <c r="E41" s="6">
+        <v>4</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H41" s="6">
+        <v>6</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J41" s="6">
+        <v>18</v>
+      </c>
+      <c r="K41" s="6">
+        <v>600</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C42" s="6">
+        <v>4007</v>
+      </c>
+      <c r="D42" s="6">
+        <v>2</v>
+      </c>
+      <c r="E42" s="6">
+        <v>4</v>
+      </c>
+      <c r="F42" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" s="6">
+        <v>7</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J42" s="6">
+        <v>18</v>
+      </c>
+      <c r="K42" s="6">
+        <v>800</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="M42" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C43" s="6">
+        <v>4008</v>
+      </c>
+      <c r="D43" s="6">
+        <v>2</v>
+      </c>
+      <c r="E43" s="6">
+        <v>4</v>
+      </c>
+      <c r="F43" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G43" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H43" s="6">
+        <v>8</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J43" s="6">
+        <v>18</v>
+      </c>
+      <c r="K43" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="M43" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C44" s="6">
+        <v>4009</v>
+      </c>
+      <c r="D44" s="6">
+        <v>2</v>
+      </c>
+      <c r="E44" s="6">
+        <v>4</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H44" s="6">
+        <v>9</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J44" s="6">
+        <v>18</v>
+      </c>
+      <c r="K44" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="M44" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C45" s="6">
+        <v>4010</v>
+      </c>
+      <c r="D45" s="6">
+        <v>2</v>
+      </c>
+      <c r="E45" s="6">
+        <v>4</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H45" s="6">
+        <v>10</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J45" s="6">
+        <v>18</v>
+      </c>
+      <c r="K45" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L45" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M45" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C46" s="6">
+        <v>5001</v>
+      </c>
+      <c r="D46" s="6">
+        <v>2</v>
+      </c>
+      <c r="E46" s="6">
+        <v>5</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H46" s="6">
+        <v>1</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="J46" s="6">
+        <v>24</v>
+      </c>
+      <c r="K46" s="6">
+        <v>100</v>
+      </c>
+      <c r="L46" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="M46" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C47" s="6">
+        <v>5002</v>
+      </c>
+      <c r="D47" s="6">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6">
+        <v>5</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="6">
+        <v>2</v>
+      </c>
+      <c r="I47" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J47" s="6">
+        <v>24</v>
+      </c>
+      <c r="K47" s="6">
+        <v>150</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="M47" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C48" s="6">
+        <v>5003</v>
+      </c>
+      <c r="D48" s="6">
+        <v>2</v>
+      </c>
+      <c r="E48" s="6">
+        <v>5</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H48" s="6">
+        <v>3</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J48" s="6">
+        <v>24</v>
+      </c>
+      <c r="K48" s="6">
+        <v>200</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M48" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C49" s="6">
+        <v>5004</v>
+      </c>
+      <c r="D49" s="6">
+        <v>2</v>
+      </c>
+      <c r="E49" s="6">
+        <v>5</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H49" s="6">
+        <v>4</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J49" s="6">
+        <v>24</v>
+      </c>
+      <c r="K49" s="6">
+        <v>300</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="M49" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="N49" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="50" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C50" s="6">
+        <v>5005</v>
+      </c>
+      <c r="D50" s="6">
+        <v>2</v>
+      </c>
+      <c r="E50" s="6">
+        <v>5</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H50" s="6">
+        <v>5</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J50" s="6">
+        <v>24</v>
+      </c>
+      <c r="K50" s="6">
+        <v>450</v>
+      </c>
+      <c r="L50" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C51" s="6">
+        <v>5006</v>
+      </c>
+      <c r="D51" s="6">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6">
+        <v>5</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="6">
+        <v>6</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J51" s="6">
+        <v>24</v>
+      </c>
+      <c r="K51" s="6">
+        <v>600</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M51" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C52" s="6">
+        <v>5007</v>
+      </c>
+      <c r="D52" s="6">
+        <v>2</v>
+      </c>
+      <c r="E52" s="6">
+        <v>5</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H52" s="6">
+        <v>7</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J52" s="6">
+        <v>24</v>
+      </c>
+      <c r="K52" s="6">
+        <v>800</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="M52" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="53" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C53" s="6">
+        <v>5008</v>
+      </c>
+      <c r="D53" s="6">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6">
+        <v>5</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H53" s="6">
+        <v>8</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J53" s="6">
+        <v>24</v>
+      </c>
+      <c r="K53" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C54" s="6">
+        <v>5009</v>
+      </c>
+      <c r="D54" s="6">
+        <v>2</v>
+      </c>
+      <c r="E54" s="6">
+        <v>5</v>
+      </c>
+      <c r="F54" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G54" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H54" s="6">
+        <v>9</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J54" s="6">
+        <v>24</v>
+      </c>
+      <c r="K54" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L54" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M54" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C55" s="6">
+        <v>5010</v>
+      </c>
+      <c r="D55" s="6">
+        <v>2</v>
+      </c>
+      <c r="E55" s="6">
+        <v>5</v>
+      </c>
+      <c r="F55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G55" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H55" s="6">
+        <v>10</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J55" s="6">
+        <v>24</v>
+      </c>
+      <c r="K55" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L55" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="M55" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="56" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C56" s="6">
+        <v>6001</v>
+      </c>
+      <c r="D56" s="6">
+        <v>2</v>
+      </c>
+      <c r="E56" s="6">
+        <v>6</v>
+      </c>
+      <c r="F56" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G56" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="H56" s="6">
+        <v>1</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J56" s="6">
+        <v>30</v>
+      </c>
+      <c r="K56" s="6">
+        <v>100</v>
+      </c>
+      <c r="L56" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="M56" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="57" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C57" s="6">
+        <v>6002</v>
+      </c>
+      <c r="D57" s="6">
+        <v>2</v>
+      </c>
+      <c r="E57" s="6">
+        <v>6</v>
+      </c>
+      <c r="F57" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="H57" s="6">
+        <v>2</v>
+      </c>
+      <c r="I57" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J57" s="6">
+        <v>30</v>
+      </c>
+      <c r="K57" s="6">
+        <v>150</v>
+      </c>
+      <c r="L57" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="58" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C58" s="6">
+        <v>6003</v>
+      </c>
+      <c r="D58" s="6">
+        <v>2</v>
+      </c>
+      <c r="E58" s="6">
+        <v>6</v>
+      </c>
+      <c r="F58" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="H58" s="6">
+        <v>3</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J58" s="6">
+        <v>30</v>
+      </c>
+      <c r="K58" s="6">
+        <v>200</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="M58" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C59" s="6">
+        <v>6004</v>
+      </c>
+      <c r="D59" s="6">
+        <v>2</v>
+      </c>
+      <c r="E59" s="6">
+        <v>6</v>
+      </c>
+      <c r="F59" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="H59" s="6">
+        <v>4</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J59" s="6">
+        <v>30</v>
+      </c>
+      <c r="K59" s="6">
+        <v>300</v>
+      </c>
+      <c r="L59" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="M59" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="60" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C60" s="6">
+        <v>6005</v>
+      </c>
+      <c r="D60" s="6">
+        <v>2</v>
+      </c>
+      <c r="E60" s="6">
+        <v>6</v>
+      </c>
+      <c r="F60" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="H60" s="6">
+        <v>5</v>
+      </c>
+      <c r="I60" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J60" s="6">
+        <v>30</v>
+      </c>
+      <c r="K60" s="6">
+        <v>450</v>
+      </c>
+      <c r="L60" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="M60" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C61" s="6">
+        <v>6006</v>
+      </c>
+      <c r="D61" s="6">
+        <v>2</v>
+      </c>
+      <c r="E61" s="6">
+        <v>6</v>
+      </c>
+      <c r="F61" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="H61" s="6">
+        <v>6</v>
+      </c>
+      <c r="I61" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J61" s="6">
+        <v>30</v>
+      </c>
+      <c r="K61" s="6">
+        <v>600</v>
+      </c>
+      <c r="L61" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="M61" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="62" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C62" s="6">
+        <v>6007</v>
+      </c>
+      <c r="D62" s="6">
+        <v>2</v>
+      </c>
+      <c r="E62" s="6">
+        <v>6</v>
+      </c>
+      <c r="F62" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G62" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H62" s="6">
+        <v>7</v>
+      </c>
+      <c r="I62" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J62" s="6">
+        <v>30</v>
+      </c>
+      <c r="K62" s="6">
+        <v>800</v>
+      </c>
+      <c r="L62" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="M62" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="63" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C63" s="6">
+        <v>6008</v>
+      </c>
+      <c r="D63" s="6">
+        <v>2</v>
+      </c>
+      <c r="E63" s="6">
+        <v>6</v>
+      </c>
+      <c r="F63" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G63" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="H63" s="6">
+        <v>8</v>
+      </c>
+      <c r="I63" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J63" s="6">
+        <v>30</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L63" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="M63" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C64" s="6">
+        <v>6009</v>
+      </c>
+      <c r="D64" s="6">
+        <v>2</v>
+      </c>
+      <c r="E64" s="6">
+        <v>6</v>
+      </c>
+      <c r="F64" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="H64" s="6">
+        <v>9</v>
+      </c>
+      <c r="I64" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J64" s="6">
+        <v>30</v>
+      </c>
+      <c r="K64" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L64" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="65" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C65" s="6">
+        <v>6010</v>
+      </c>
+      <c r="D65" s="6">
+        <v>2</v>
+      </c>
+      <c r="E65" s="6">
+        <v>6</v>
+      </c>
+      <c r="F65" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="G65" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65" s="6">
+        <v>10</v>
+      </c>
+      <c r="I65" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J65" s="6">
+        <v>30</v>
+      </c>
+      <c r="K65" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="M65" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="66" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C66" s="6">
+        <v>7001</v>
+      </c>
+      <c r="D66" s="6">
+        <v>3</v>
+      </c>
+      <c r="E66" s="6">
+        <v>7</v>
+      </c>
+      <c r="F66" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G66" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H66" s="6">
+        <v>1</v>
+      </c>
+      <c r="I66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J66" s="6">
+        <v>0</v>
+      </c>
+      <c r="K66" s="6">
+        <v>100</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="M66" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="N66" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="67" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C67" s="6">
+        <v>7002</v>
+      </c>
+      <c r="D67" s="6">
+        <v>3</v>
+      </c>
+      <c r="E67" s="6">
+        <v>7</v>
+      </c>
+      <c r="F67" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G67" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H67" s="6">
+        <v>2</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J67" s="6">
+        <v>0</v>
+      </c>
+      <c r="K67" s="6">
+        <v>150</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="M67" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C68" s="6">
+        <v>7003</v>
+      </c>
+      <c r="D68" s="6">
+        <v>3</v>
+      </c>
+      <c r="E68" s="6">
+        <v>7</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H68" s="6">
+        <v>3</v>
+      </c>
+      <c r="I68" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J68" s="6">
+        <v>0</v>
+      </c>
+      <c r="K68" s="6">
+        <v>200</v>
+      </c>
+      <c r="L68" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="M68" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="N68" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="69" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C69" s="6">
+        <v>7004</v>
+      </c>
+      <c r="D69" s="6">
+        <v>3</v>
+      </c>
+      <c r="E69" s="6">
+        <v>7</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G69" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H69" s="6">
+        <v>4</v>
+      </c>
+      <c r="I69" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J69" s="6">
+        <v>0</v>
+      </c>
+      <c r="K69" s="6">
+        <v>300</v>
+      </c>
+      <c r="L69" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M69" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="70" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C70" s="6">
+        <v>7005</v>
+      </c>
+      <c r="D70" s="6">
+        <v>3</v>
+      </c>
+      <c r="E70" s="6">
+        <v>7</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H70" s="6">
+        <v>5</v>
+      </c>
+      <c r="I70" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J70" s="6">
+        <v>0</v>
+      </c>
+      <c r="K70" s="6">
+        <v>450</v>
+      </c>
+      <c r="L70" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="M70" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="71" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C71" s="6">
+        <v>7006</v>
+      </c>
+      <c r="D71" s="6">
+        <v>3</v>
+      </c>
+      <c r="E71" s="6">
+        <v>7</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H71" s="6">
+        <v>6</v>
+      </c>
+      <c r="I71" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J71" s="6">
+        <v>0</v>
+      </c>
+      <c r="K71" s="6">
+        <v>600</v>
+      </c>
+      <c r="L71" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M71" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="N71" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="72" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C72" s="6">
+        <v>7007</v>
+      </c>
+      <c r="D72" s="6">
+        <v>3</v>
+      </c>
+      <c r="E72" s="6">
+        <v>7</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G72" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H72" s="6">
+        <v>7</v>
+      </c>
+      <c r="I72" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J72" s="6">
+        <v>0</v>
+      </c>
+      <c r="K72" s="6">
+        <v>800</v>
+      </c>
+      <c r="L72" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="M72" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="N72" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C73" s="6">
+        <v>7008</v>
+      </c>
+      <c r="D73" s="6">
+        <v>3</v>
+      </c>
+      <c r="E73" s="6">
+        <v>7</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H73" s="6">
+        <v>8</v>
+      </c>
+      <c r="I73" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J73" s="6">
+        <v>0</v>
+      </c>
+      <c r="K73" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L73" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C74" s="6">
+        <v>7009</v>
+      </c>
+      <c r="D74" s="6">
+        <v>3</v>
+      </c>
+      <c r="E74" s="6">
+        <v>7</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G74" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H74" s="6">
+        <v>9</v>
+      </c>
+      <c r="I74" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J74" s="6">
+        <v>0</v>
+      </c>
+      <c r="K74" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="M74" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="N74" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="75" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C75" s="6">
+        <v>7010</v>
+      </c>
+      <c r="D75" s="6">
+        <v>3</v>
+      </c>
+      <c r="E75" s="6">
+        <v>7</v>
+      </c>
+      <c r="F75" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J27" s="6">
+      <c r="G75" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H75" s="6">
+        <v>10</v>
+      </c>
+      <c r="I75" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J75" s="6">
+        <v>0</v>
+      </c>
+      <c r="K75" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L75" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="M75" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="N75" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="76" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C76" s="6">
+        <v>8001</v>
+      </c>
+      <c r="D76" s="6">
+        <v>3</v>
+      </c>
+      <c r="E76" s="6">
         <v>8</v>
       </c>
-      <c r="K27" s="6">
-        <v>130</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M27" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N27" s="7" t="s">
+      <c r="F76" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H76" s="6">
+        <v>1</v>
+      </c>
+      <c r="I76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J76" s="6">
+        <v>0</v>
+      </c>
+      <c r="K76" s="6">
+        <v>100</v>
+      </c>
+      <c r="L76" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M76" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="N76" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C77" s="6">
+        <v>8002</v>
+      </c>
+      <c r="D77" s="6">
+        <v>3</v>
+      </c>
+      <c r="E77" s="6">
+        <v>8</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G77" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H77" s="6">
+        <v>2</v>
+      </c>
+      <c r="I77" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J77" s="6">
+        <v>0</v>
+      </c>
+      <c r="K77" s="6">
+        <v>150</v>
+      </c>
+      <c r="L77" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="M77" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="N77" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="78" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C78" s="6">
+        <v>8003</v>
+      </c>
+      <c r="D78" s="6">
+        <v>3</v>
+      </c>
+      <c r="E78" s="6">
+        <v>8</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G78" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H78" s="6">
+        <v>3</v>
+      </c>
+      <c r="I78" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J78" s="6">
+        <v>0</v>
+      </c>
+      <c r="K78" s="6">
+        <v>200</v>
+      </c>
+      <c r="L78" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M78" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="N78" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="79" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C79" s="6">
+        <v>8004</v>
+      </c>
+      <c r="D79" s="6">
+        <v>3</v>
+      </c>
+      <c r="E79" s="6">
+        <v>8</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G79" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H79" s="6">
+        <v>4</v>
+      </c>
+      <c r="I79" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J79" s="6">
+        <v>0</v>
+      </c>
+      <c r="K79" s="6">
+        <v>300</v>
+      </c>
+      <c r="L79" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="M79" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="80" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C80" s="6">
+        <v>8005</v>
+      </c>
+      <c r="D80" s="6">
+        <v>3</v>
+      </c>
+      <c r="E80" s="6">
+        <v>8</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H80" s="6">
+        <v>5</v>
+      </c>
+      <c r="I80" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J80" s="6">
+        <v>0</v>
+      </c>
+      <c r="K80" s="6">
+        <v>450</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C81" s="6">
+        <v>8006</v>
+      </c>
+      <c r="D81" s="6">
+        <v>3</v>
+      </c>
+      <c r="E81" s="6">
+        <v>8</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G81" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H81" s="6">
+        <v>6</v>
+      </c>
+      <c r="I81" s="8" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="28" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C28" s="6">
-        <v>6001</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="J81" s="6">
+        <v>0</v>
+      </c>
+      <c r="K81" s="6">
+        <v>600</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M81" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="82" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C82" s="6">
+        <v>8007</v>
+      </c>
+      <c r="D82" s="6">
+        <v>3</v>
+      </c>
+      <c r="E82" s="6">
+        <v>8</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H82" s="6">
+        <v>7</v>
+      </c>
+      <c r="I82" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J82" s="6">
+        <v>0</v>
+      </c>
+      <c r="K82" s="6">
+        <v>800</v>
+      </c>
+      <c r="L82" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="M82" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="83" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C83" s="6">
+        <v>8008</v>
+      </c>
+      <c r="D83" s="6">
+        <v>3</v>
+      </c>
+      <c r="E83" s="6">
+        <v>8</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G83" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H83" s="6">
+        <v>8</v>
+      </c>
+      <c r="I83" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J83" s="6">
+        <v>0</v>
+      </c>
+      <c r="K83" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L83" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="M83" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="N83" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="84" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C84" s="6">
+        <v>8009</v>
+      </c>
+      <c r="D84" s="6">
+        <v>3</v>
+      </c>
+      <c r="E84" s="6">
+        <v>8</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G84" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H84" s="6">
+        <v>9</v>
+      </c>
+      <c r="I84" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J84" s="6">
+        <v>0</v>
+      </c>
+      <c r="K84" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L84" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="M84" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="N84" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C85" s="6">
+        <v>8010</v>
+      </c>
+      <c r="D85" s="6">
+        <v>3</v>
+      </c>
+      <c r="E85" s="6">
+        <v>8</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G85" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H85" s="6">
+        <v>10</v>
+      </c>
+      <c r="I85" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J85" s="6">
+        <v>0</v>
+      </c>
+      <c r="K85" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L85" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="M85" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="N85" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C86" s="6">
+        <v>9001</v>
+      </c>
+      <c r="D86" s="6">
+        <v>3</v>
+      </c>
+      <c r="E86" s="6">
+        <v>9</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="G86" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H86" s="6">
+        <v>1</v>
+      </c>
+      <c r="I86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="J86" s="6">
+        <v>0</v>
+      </c>
+      <c r="K86" s="6">
+        <v>100</v>
+      </c>
+      <c r="L86" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="M86" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="N86" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C87" s="6">
+        <v>9002</v>
+      </c>
+      <c r="D87" s="6">
+        <v>3</v>
+      </c>
+      <c r="E87" s="6">
+        <v>9</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H87" s="6">
         <v>2</v>
       </c>
-      <c r="E28" s="6">
+      <c r="I87" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="J87" s="6">
+        <v>0</v>
+      </c>
+      <c r="K87" s="6">
+        <v>150</v>
+      </c>
+      <c r="L87" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="M87" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="N87" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C88" s="6">
+        <v>9003</v>
+      </c>
+      <c r="D88" s="6">
+        <v>3</v>
+      </c>
+      <c r="E88" s="6">
+        <v>9</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H88" s="6">
+        <v>3</v>
+      </c>
+      <c r="I88" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J88" s="6">
+        <v>0</v>
+      </c>
+      <c r="K88" s="6">
+        <v>200</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="M88" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="N88" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C89" s="6">
+        <v>9004</v>
+      </c>
+      <c r="D89" s="6">
+        <v>3</v>
+      </c>
+      <c r="E89" s="6">
+        <v>9</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G89" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H89" s="6">
+        <v>4</v>
+      </c>
+      <c r="I89" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J89" s="6">
+        <v>0</v>
+      </c>
+      <c r="K89" s="6">
+        <v>300</v>
+      </c>
+      <c r="L89" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M89" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="N89" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="90" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C90" s="6">
+        <v>9005</v>
+      </c>
+      <c r="D90" s="6">
+        <v>3</v>
+      </c>
+      <c r="E90" s="6">
+        <v>9</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="G90" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H90" s="6">
+        <v>5</v>
+      </c>
+      <c r="I90" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J90" s="6">
+        <v>0</v>
+      </c>
+      <c r="K90" s="6">
+        <v>450</v>
+      </c>
+      <c r="L90" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="M90" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="N90" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="91" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C91" s="6">
+        <v>9006</v>
+      </c>
+      <c r="D91" s="6">
+        <v>3</v>
+      </c>
+      <c r="E91" s="6">
+        <v>9</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H91" s="6">
         <v>6</v>
       </c>
-      <c r="F28" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6">
-        <v>1</v>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="J28" s="6">
+      <c r="I91" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="J91" s="6">
+        <v>0</v>
+      </c>
+      <c r="K91" s="6">
+        <v>600</v>
+      </c>
+      <c r="L91" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="M91" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="N91" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C92" s="6">
+        <v>9007</v>
+      </c>
+      <c r="D92" s="6">
+        <v>3</v>
+      </c>
+      <c r="E92" s="6">
+        <v>9</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H92" s="6">
         <v>7</v>
       </c>
-      <c r="K28" s="6">
-        <v>140</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M28" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="29" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C29" s="6">
-        <v>6002</v>
-      </c>
-      <c r="D29" s="6">
-        <v>2</v>
-      </c>
-      <c r="E29" s="6">
-        <v>6</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H29" s="6">
-        <v>2</v>
-      </c>
-      <c r="I29" s="8" t="s">
+      <c r="I92" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J92" s="6">
+        <v>0</v>
+      </c>
+      <c r="K92" s="6">
+        <v>800</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="M92" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="N92" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C93" s="6">
+        <v>9008</v>
+      </c>
+      <c r="D93" s="6">
+        <v>3</v>
+      </c>
+      <c r="E93" s="6">
+        <v>9</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H93" s="6">
+        <v>8</v>
+      </c>
+      <c r="I93" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J93" s="6">
+        <v>0</v>
+      </c>
+      <c r="K93" s="6">
+        <v>1000</v>
+      </c>
+      <c r="L93" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="M93" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="N93" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C94" s="6">
+        <v>9009</v>
+      </c>
+      <c r="D94" s="6">
+        <v>3</v>
+      </c>
+      <c r="E94" s="6">
+        <v>9</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H94" s="6">
+        <v>9</v>
+      </c>
+      <c r="I94" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J94" s="6">
+        <v>0</v>
+      </c>
+      <c r="K94" s="6">
+        <v>1200</v>
+      </c>
+      <c r="L94" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="M94" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="N94" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C95" s="6">
+        <v>9010</v>
+      </c>
+      <c r="D95" s="6">
+        <v>3</v>
+      </c>
+      <c r="E95" s="6">
+        <v>9</v>
+      </c>
+      <c r="F95" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="J29" s="6">
-        <v>8</v>
-      </c>
-      <c r="K29" s="6">
-        <v>150</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M29" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N29" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C30" s="6">
-        <v>7001</v>
-      </c>
-      <c r="D30" s="6">
-        <v>3</v>
-      </c>
-      <c r="E30" s="6">
-        <v>7</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6">
-        <v>1</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J30" s="6">
-        <v>7</v>
-      </c>
-      <c r="K30" s="6">
-        <v>160</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M30" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C31" s="6">
-        <v>7002</v>
-      </c>
-      <c r="D31" s="6">
-        <v>3</v>
-      </c>
-      <c r="E31" s="6">
-        <v>7</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H31" s="6">
-        <v>2</v>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J31" s="6">
-        <v>8</v>
-      </c>
-      <c r="K31" s="6">
-        <v>170</v>
-      </c>
-      <c r="L31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M31" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N31" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="32" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C32" s="6">
-        <v>8001</v>
-      </c>
-      <c r="D32" s="6">
-        <v>3</v>
-      </c>
-      <c r="E32" s="6">
-        <v>8</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H32" s="6">
-        <v>1</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J32" s="6">
-        <v>7</v>
-      </c>
-      <c r="K32" s="6">
-        <v>180</v>
-      </c>
-      <c r="L32" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M32" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N32" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C33" s="6">
-        <v>8002</v>
-      </c>
-      <c r="D33" s="6">
-        <v>3</v>
-      </c>
-      <c r="E33" s="6">
-        <v>8</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G33" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H33" s="6">
-        <v>2</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J33" s="6">
-        <v>8</v>
-      </c>
-      <c r="K33" s="6">
-        <v>190</v>
-      </c>
-      <c r="L33" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M33" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N33" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="34" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C34" s="6">
-        <v>9001</v>
-      </c>
-      <c r="D34" s="6">
-        <v>3</v>
-      </c>
-      <c r="E34" s="6">
-        <v>9</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H34" s="6">
-        <v>1</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="J34" s="6">
-        <v>7</v>
-      </c>
-      <c r="K34" s="6">
-        <v>200</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="M34" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="N34" s="7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="35" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C35" s="6">
-        <v>9002</v>
-      </c>
-      <c r="D35" s="6">
-        <v>3</v>
-      </c>
-      <c r="E35" s="6">
-        <v>9</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="6">
-        <v>2</v>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J35" s="6">
-        <v>8</v>
-      </c>
-      <c r="K35" s="6">
-        <v>210</v>
-      </c>
-      <c r="L35" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="M35" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="N35" s="7" t="s">
-        <v>37</v>
+      <c r="G95" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="H95" s="6">
+        <v>10</v>
+      </c>
+      <c r="I95" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="J95" s="6">
+        <v>0</v>
+      </c>
+      <c r="K95" s="6">
+        <v>1500</v>
+      </c>
+      <c r="L95" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="M95" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="N95" s="7" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{854C9324-9217-40F1-B4CC-A33B64F0C165}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2868E6EB-E56E-4C99-87E3-64B6A4CA17F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MagickaSlotProto" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="277">
   <si>
     <t>c</t>
   </si>
@@ -665,36 +665,6 @@
     <t>魔法提升240点;血量提升600点</t>
   </si>
   <si>
-    <t>血量提升25点;物防提升5点点;魔防提升5点</t>
-  </si>
-  <si>
-    <t>血量提升60点;物防提升10点点;魔防提升10点</t>
-  </si>
-  <si>
-    <t>血量提升100点;物防提升15点点;魔防提升15点</t>
-  </si>
-  <si>
-    <t>血量提升150点;物防提升20点点;魔防提升20点</t>
-  </si>
-  <si>
-    <t>血量提升225点;物防提升30点点;魔防提升30点</t>
-  </si>
-  <si>
-    <t>血量提升300点;物防提升40点点;魔防提升40点</t>
-  </si>
-  <si>
-    <t>血量提升375点;物防提升50点点;魔防提升50点</t>
-  </si>
-  <si>
-    <t>血量提升450点;物防提升60点点;魔防提升60点</t>
-  </si>
-  <si>
-    <t>血量提升525点;物防提升70点点;魔防提升70点</t>
-  </si>
-  <si>
-    <t>血量提升600点;物防提升80点点;魔防提升80点</t>
-  </si>
-  <si>
     <t>Attack +10; Physical Defense +10</t>
   </si>
   <si>
@@ -845,34 +815,96 @@
     <t>Magic +240; HP +600</t>
   </si>
   <si>
-    <t>HP +25; Physical Defense +5; Magical Defense +5</t>
-  </si>
-  <si>
-    <t>HP +60; Physical Defense +10; Magical Defense +10</t>
-  </si>
-  <si>
-    <t>HP +100; Physical Defense +15; Magical Defense +15</t>
-  </si>
-  <si>
-    <t>HP +150; Physical Defense +20; Magical Defense +20</t>
-  </si>
-  <si>
-    <t>HP +225; Physical Defense +30; Magical Defense +30</t>
-  </si>
-  <si>
-    <t>HP +300; Physical Defense +40; Magical Defense +40</t>
-  </si>
-  <si>
-    <t>HP +375; Physical Defense +50; Magical Defense +50</t>
-  </si>
-  <si>
-    <t>HP +450; Physical Defense +60; Magical Defense +60</t>
-  </si>
-  <si>
-    <t>HP +525; Physical Defense +70; Magical Defense +70</t>
-  </si>
-  <si>
-    <t>HP +600; Physical Defense +80; Magical Defense +80</t>
+    <t>血量提升150点;物防和魔防提升20点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升25点;物防和魔防提升5点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升60点;物防和魔防提升10点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升100点;物防和魔防提升15点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升225点;物防和魔防提升30点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升375点;物防和魔防提升50点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升300点;物防和魔防提升40点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升450点;物防和魔防提升60点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升525点;物防和魔防提升70点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量提升600点;物防和魔防提升80点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack +10; Physical Defense +10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +25; All Defense +5</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +60; All Defense +10</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +100;All Defense +15</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +150;All Defense +20</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +225;All Defense +30</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +300;All Defense +40</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +375;All Defense +50</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +450;All Defense +60</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +525;All Defense +70</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +600;All Defense +80</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack +240; Physical Defense +240</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击提升10点;物防提升10点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3004,7 +3036,7 @@
         <v>154</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3042,7 +3074,7 @@
         <v>155</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3080,7 +3112,7 @@
         <v>156</v>
       </c>
       <c r="N8" s="7" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3118,7 +3150,7 @@
         <v>157</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3156,7 +3188,7 @@
         <v>158</v>
       </c>
       <c r="N10" s="7" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3194,7 +3226,7 @@
         <v>159</v>
       </c>
       <c r="N11" s="7" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3232,7 +3264,7 @@
         <v>160</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3270,7 +3302,7 @@
         <v>161</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3308,7 +3340,7 @@
         <v>162</v>
       </c>
       <c r="N14" s="7" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3346,7 +3378,7 @@
         <v>163</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="16" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3384,7 +3416,7 @@
         <v>164</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3422,7 +3454,7 @@
         <v>165</v>
       </c>
       <c r="N17" s="7" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3460,7 +3492,7 @@
         <v>166</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3498,7 +3530,7 @@
         <v>167</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3536,7 +3568,7 @@
         <v>168</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3574,7 +3606,7 @@
         <v>169</v>
       </c>
       <c r="N21" s="7" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3612,7 +3644,7 @@
         <v>170</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3650,7 +3682,7 @@
         <v>171</v>
       </c>
       <c r="N23" s="7" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3688,7 +3720,7 @@
         <v>172</v>
       </c>
       <c r="N24" s="7" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3726,7 +3758,7 @@
         <v>173</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3764,7 +3796,7 @@
         <v>174</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3802,7 +3834,7 @@
         <v>175</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3840,7 +3872,7 @@
         <v>176</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3879,7 +3911,7 @@
         <v>177</v>
       </c>
       <c r="N29" s="7" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3917,7 +3949,7 @@
         <v>178</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3956,7 +3988,7 @@
         <v>179</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -3994,7 +4026,7 @@
         <v>180</v>
       </c>
       <c r="N32" s="7" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4033,7 +4065,7 @@
         <v>181</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4071,7 +4103,7 @@
         <v>182</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4110,7 +4142,7 @@
         <v>183</v>
       </c>
       <c r="N35" s="7" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4148,7 +4180,7 @@
         <v>184</v>
       </c>
       <c r="N36" s="7" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4186,7 +4218,7 @@
         <v>185</v>
       </c>
       <c r="N37" s="7" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4224,7 +4256,7 @@
         <v>186</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4262,7 +4294,7 @@
         <v>187</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4300,7 +4332,7 @@
         <v>188</v>
       </c>
       <c r="N40" s="7" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4338,7 +4370,7 @@
         <v>189</v>
       </c>
       <c r="N41" s="7" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4376,7 +4408,7 @@
         <v>190</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4414,7 +4446,7 @@
         <v>191</v>
       </c>
       <c r="N43" s="7" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4452,7 +4484,7 @@
         <v>192</v>
       </c>
       <c r="N44" s="7" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4490,7 +4522,7 @@
         <v>193</v>
       </c>
       <c r="N45" s="7" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4528,7 +4560,7 @@
         <v>194</v>
       </c>
       <c r="N46" s="7" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4566,7 +4598,7 @@
         <v>195</v>
       </c>
       <c r="N47" s="7" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4604,7 +4636,7 @@
         <v>196</v>
       </c>
       <c r="N48" s="7" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4642,7 +4674,7 @@
         <v>197</v>
       </c>
       <c r="N49" s="7" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="50" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4680,7 +4712,7 @@
         <v>198</v>
       </c>
       <c r="N50" s="7" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4718,7 +4750,7 @@
         <v>199</v>
       </c>
       <c r="N51" s="7" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4756,7 +4788,7 @@
         <v>200</v>
       </c>
       <c r="N52" s="7" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="53" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4794,7 +4826,7 @@
         <v>201</v>
       </c>
       <c r="N53" s="7" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="54" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4832,7 +4864,7 @@
         <v>202</v>
       </c>
       <c r="N54" s="7" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="55" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4870,7 +4902,7 @@
         <v>203</v>
       </c>
       <c r="N55" s="7" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="56" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4905,10 +4937,10 @@
         <v>144</v>
       </c>
       <c r="M56" s="7" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
       <c r="N56" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="57" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4943,10 +4975,10 @@
         <v>145</v>
       </c>
       <c r="M57" s="7" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="N57" s="7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="58" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -4981,10 +5013,10 @@
         <v>146</v>
       </c>
       <c r="M58" s="7" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="N58" s="7" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="59" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5019,10 +5051,10 @@
         <v>147</v>
       </c>
       <c r="M59" s="7" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
       <c r="N59" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="60" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5057,10 +5089,10 @@
         <v>148</v>
       </c>
       <c r="M60" s="7" t="s">
-        <v>208</v>
+        <v>258</v>
       </c>
       <c r="N60" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5095,10 +5127,10 @@
         <v>149</v>
       </c>
       <c r="M61" s="7" t="s">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="N61" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5133,10 +5165,10 @@
         <v>150</v>
       </c>
       <c r="M62" s="7" t="s">
-        <v>210</v>
+        <v>259</v>
       </c>
       <c r="N62" s="7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="63" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5171,10 +5203,10 @@
         <v>151</v>
       </c>
       <c r="M63" s="7" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="N63" s="7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="64" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5209,10 +5241,10 @@
         <v>152</v>
       </c>
       <c r="M64" s="7" t="s">
-        <v>212</v>
+        <v>262</v>
       </c>
       <c r="N64" s="7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="65" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5247,10 +5279,10 @@
         <v>153</v>
       </c>
       <c r="M65" s="7" t="s">
-        <v>213</v>
+        <v>263</v>
       </c>
       <c r="N65" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="66" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5285,10 +5317,10 @@
         <v>93</v>
       </c>
       <c r="M66" s="7" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="N66" s="7" t="s">
-        <v>214</v>
+        <v>264</v>
       </c>
     </row>
     <row r="67" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5326,7 +5358,7 @@
         <v>155</v>
       </c>
       <c r="N67" s="7" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5364,7 +5396,7 @@
         <v>156</v>
       </c>
       <c r="N68" s="7" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
     </row>
     <row r="69" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5402,7 +5434,7 @@
         <v>157</v>
       </c>
       <c r="N69" s="7" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
     </row>
     <row r="70" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5440,7 +5472,7 @@
         <v>158</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
     </row>
     <row r="71" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5478,7 +5510,7 @@
         <v>159</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
     </row>
     <row r="72" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5516,7 +5548,7 @@
         <v>160</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
     </row>
     <row r="73" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5554,7 +5586,7 @@
         <v>161</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5592,7 +5624,7 @@
         <v>162</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="75" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5630,7 +5662,7 @@
         <v>163</v>
       </c>
       <c r="N75" s="7" t="s">
-        <v>223</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5668,7 +5700,7 @@
         <v>164</v>
       </c>
       <c r="N76" s="7" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="77" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5706,7 +5738,7 @@
         <v>165</v>
       </c>
       <c r="N77" s="7" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
     </row>
     <row r="78" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5744,7 +5776,7 @@
         <v>166</v>
       </c>
       <c r="N78" s="7" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="79" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5782,7 +5814,7 @@
         <v>167</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="80" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5820,7 +5852,7 @@
         <v>168</v>
       </c>
       <c r="N80" s="7" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
     </row>
     <row r="81" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5858,7 +5890,7 @@
         <v>169</v>
       </c>
       <c r="N81" s="7" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="82" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5896,7 +5928,7 @@
         <v>170</v>
       </c>
       <c r="N82" s="7" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="83" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5934,7 +5966,7 @@
         <v>171</v>
       </c>
       <c r="N83" s="7" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="84" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -5972,7 +6004,7 @@
         <v>172</v>
       </c>
       <c r="N84" s="7" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="85" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6010,7 +6042,7 @@
         <v>173</v>
       </c>
       <c r="N85" s="7" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="86" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6048,7 +6080,7 @@
         <v>174</v>
       </c>
       <c r="N86" s="7" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="87" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6086,7 +6118,7 @@
         <v>175</v>
       </c>
       <c r="N87" s="7" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="88" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6124,7 +6156,7 @@
         <v>176</v>
       </c>
       <c r="N88" s="7" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6162,7 +6194,7 @@
         <v>177</v>
       </c>
       <c r="N89" s="7" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="90" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6200,7 +6232,7 @@
         <v>178</v>
       </c>
       <c r="N90" s="7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="91" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6238,7 +6270,7 @@
         <v>179</v>
       </c>
       <c r="N91" s="7" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
     </row>
     <row r="92" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6276,7 +6308,7 @@
         <v>180</v>
       </c>
       <c r="N92" s="7" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="93" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6314,7 +6346,7 @@
         <v>181</v>
       </c>
       <c r="N93" s="7" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
     </row>
     <row r="94" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6352,7 +6384,7 @@
         <v>182</v>
       </c>
       <c r="N94" s="7" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="95" spans="3:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -6390,7 +6422,7 @@
         <v>183</v>
       </c>
       <c r="N95" s="7" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2868E6EB-E56E-4C99-87E3-64B6A4CA17F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69868C75-365C-42C8-80EC-DACBB804CA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3401,10 +3401,10 @@
         <v>1</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="J16" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K16" s="6">
         <v>100</v>
@@ -3442,7 +3442,7 @@
         <v>33</v>
       </c>
       <c r="J17" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K17" s="6">
         <v>150</v>
@@ -3480,7 +3480,7 @@
         <v>34</v>
       </c>
       <c r="J18" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K18" s="6">
         <v>200</v>
@@ -3518,7 +3518,7 @@
         <v>35</v>
       </c>
       <c r="J19" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K19" s="6">
         <v>300</v>
@@ -3556,7 +3556,7 @@
         <v>36</v>
       </c>
       <c r="J20" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K20" s="6">
         <v>450</v>
@@ -3594,7 +3594,7 @@
         <v>37</v>
       </c>
       <c r="J21" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K21" s="6">
         <v>600</v>
@@ -3632,7 +3632,7 @@
         <v>38</v>
       </c>
       <c r="J22" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K22" s="6">
         <v>800</v>
@@ -3670,7 +3670,7 @@
         <v>39</v>
       </c>
       <c r="J23" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K23" s="6">
         <v>1000</v>
@@ -3708,7 +3708,7 @@
         <v>40</v>
       </c>
       <c r="J24" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K24" s="6">
         <v>1200</v>
@@ -3746,7 +3746,7 @@
         <v>41</v>
       </c>
       <c r="J25" s="6">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K25" s="6">
         <v>1500</v>
@@ -3781,10 +3781,10 @@
         <v>1</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J26" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K26" s="6">
         <v>100</v>
@@ -3822,7 +3822,7 @@
         <v>33</v>
       </c>
       <c r="J27" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K27" s="6">
         <v>150</v>
@@ -3860,7 +3860,7 @@
         <v>34</v>
       </c>
       <c r="J28" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K28" s="6">
         <v>200</v>
@@ -3899,7 +3899,7 @@
         <v>35</v>
       </c>
       <c r="J29" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K29" s="6">
         <v>300</v>
@@ -3937,7 +3937,7 @@
         <v>36</v>
       </c>
       <c r="J30" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K30" s="6">
         <v>450</v>
@@ -3976,7 +3976,7 @@
         <v>37</v>
       </c>
       <c r="J31" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K31" s="6">
         <v>600</v>
@@ -4014,7 +4014,7 @@
         <v>38</v>
       </c>
       <c r="J32" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K32" s="6">
         <v>800</v>
@@ -4053,7 +4053,7 @@
         <v>39</v>
       </c>
       <c r="J33" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K33" s="6">
         <v>1000</v>
@@ -4091,7 +4091,7 @@
         <v>40</v>
       </c>
       <c r="J34" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K34" s="6">
         <v>1200</v>
@@ -4130,7 +4130,7 @@
         <v>41</v>
       </c>
       <c r="J35" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K35" s="6">
         <v>1500</v>
@@ -4165,10 +4165,10 @@
         <v>1</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J36" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K36" s="6">
         <v>100</v>
@@ -4206,7 +4206,7 @@
         <v>33</v>
       </c>
       <c r="J37" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K37" s="6">
         <v>150</v>
@@ -4244,7 +4244,7 @@
         <v>34</v>
       </c>
       <c r="J38" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K38" s="6">
         <v>200</v>
@@ -4282,7 +4282,7 @@
         <v>35</v>
       </c>
       <c r="J39" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K39" s="6">
         <v>300</v>
@@ -4320,7 +4320,7 @@
         <v>36</v>
       </c>
       <c r="J40" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K40" s="6">
         <v>450</v>
@@ -4358,7 +4358,7 @@
         <v>37</v>
       </c>
       <c r="J41" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K41" s="6">
         <v>600</v>
@@ -4396,7 +4396,7 @@
         <v>38</v>
       </c>
       <c r="J42" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K42" s="6">
         <v>800</v>
@@ -4434,7 +4434,7 @@
         <v>39</v>
       </c>
       <c r="J43" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K43" s="6">
         <v>1000</v>
@@ -4472,7 +4472,7 @@
         <v>40</v>
       </c>
       <c r="J44" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K44" s="6">
         <v>1200</v>
@@ -4510,7 +4510,7 @@
         <v>41</v>
       </c>
       <c r="J45" s="6">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="K45" s="6">
         <v>1500</v>
@@ -4545,10 +4545,10 @@
         <v>1</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J46" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K46" s="6">
         <v>100</v>
@@ -4586,7 +4586,7 @@
         <v>33</v>
       </c>
       <c r="J47" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K47" s="6">
         <v>150</v>
@@ -4624,7 +4624,7 @@
         <v>34</v>
       </c>
       <c r="J48" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K48" s="6">
         <v>200</v>
@@ -4662,7 +4662,7 @@
         <v>35</v>
       </c>
       <c r="J49" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K49" s="6">
         <v>300</v>
@@ -4700,7 +4700,7 @@
         <v>36</v>
       </c>
       <c r="J50" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K50" s="6">
         <v>450</v>
@@ -4738,7 +4738,7 @@
         <v>37</v>
       </c>
       <c r="J51" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K51" s="6">
         <v>600</v>
@@ -4776,7 +4776,7 @@
         <v>38</v>
       </c>
       <c r="J52" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K52" s="6">
         <v>800</v>
@@ -4814,7 +4814,7 @@
         <v>39</v>
       </c>
       <c r="J53" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K53" s="6">
         <v>1000</v>
@@ -4852,7 +4852,7 @@
         <v>40</v>
       </c>
       <c r="J54" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K54" s="6">
         <v>1200</v>
@@ -4890,7 +4890,7 @@
         <v>41</v>
       </c>
       <c r="J55" s="6">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K55" s="6">
         <v>1500</v>

--- a/Excel/MagickaSlotConfig.xlsx
+++ b/Excel/MagickaSlotConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69868C75-365C-42C8-80EC-DACBB804CA6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB718099-9BDF-4D69-9831-C155E0174EAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="279">
   <si>
     <t>c</t>
   </si>
@@ -904,6 +904,14 @@
   </si>
   <si>
     <t>攻击提升10点;物防提升10点</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000181;2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000181;3</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -5685,7 +5693,7 @@
         <v>1</v>
       </c>
       <c r="I76" s="6" t="s">
-        <v>26</v>
+        <v>277</v>
       </c>
       <c r="J76" s="6">
         <v>0</v>
@@ -6065,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>26</v>
+        <v>278</v>
       </c>
       <c r="J86" s="6">
         <v>0</v>
